--- a/data/trans_orig/P17G-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/P17G-Estudios-trans_orig.xlsx
@@ -538,7 +538,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según era el médico al que consultó en la última visita en 2007</t>
+          <t>Población según a dónde pertenecía el/a médico/a al que consultó en las últimas 2 semanas en 2007 (tasa de respuesta: 99,82%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -733,97 +733,97 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>1859</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>0,56%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
+      <c r="O4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q4" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="K4" s="2" t="inlineStr">
+      <c r="R4" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>1950</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
+      <c r="S4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="T4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="U4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O4" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P4" s="2" t="inlineStr">
-        <is>
-          <t>0,37%</t>
-        </is>
-      </c>
-      <c r="Q4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="R4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T4" s="2" t="inlineStr">
-        <is>
-          <t>1916</t>
-        </is>
-      </c>
-      <c r="U4" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>0,22%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>2771</t>
+          <t>2905</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>12289</t>
+          <t>13990</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,83%</t>
+          <t>0,87%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>3,68%</t>
+          <t>4,19%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -886,7 +886,7 @@
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>4857</t>
+          <t>6225</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -901,7 +901,7 @@
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>0,92%</t>
+          <t>1,18%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>3655</t>
+          <t>3602</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>14799</t>
+          <t>14831</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -959,12 +959,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>1702</t>
+          <t>1689</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>10012</t>
+          <t>10407</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -979,7 +979,7 @@
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>3,0%</t>
+          <t>3,11%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -999,7 +999,7 @@
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>8498</t>
+          <t>8101</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1014,7 +1014,7 @@
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>1,61%</t>
+          <t>1,53%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1029,12 +1029,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>2948</t>
+          <t>2900</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>13943</t>
+          <t>13992</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1077,7 +1077,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>7380</t>
+          <t>6743</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1092,7 +1092,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>2,21%</t>
+          <t>2,02%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1107,12 +1107,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>3330</t>
+          <t>2926</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>15405</t>
+          <t>14571</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1122,12 +1122,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>0,63%</t>
+          <t>0,55%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>2,92%</t>
+          <t>2,76%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1142,12 +1142,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>4425</t>
+          <t>4781</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>17655</t>
+          <t>17509</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1157,12 +1157,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,51%</t>
+          <t>0,55%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>2,05%</t>
+          <t>2,03%</t>
         </is>
       </c>
     </row>
@@ -1185,12 +1185,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>313253</t>
+          <t>311754</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>326866</t>
+          <t>326238</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1200,12 +1200,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>93,74%</t>
+          <t>93,29%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>97,81%</t>
+          <t>97,62%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1220,12 +1220,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>508638</t>
+          <t>508932</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>522395</t>
+          <t>523059</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1235,12 +1235,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>96,32%</t>
+          <t>96,38%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>98,93%</t>
+          <t>99,05%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1255,12 +1255,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>827414</t>
+          <t>826834</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>846741</t>
+          <t>846885</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1270,12 +1270,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>95,96%</t>
+          <t>95,89%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>98,2%</t>
+          <t>98,22%</t>
         </is>
       </c>
     </row>
@@ -1415,97 +1415,97 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>1926</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>0,77%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
+      <c r="O10" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P10" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q10" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="K10" s="2" t="inlineStr">
+      <c r="R10" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>1974</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
+      <c r="S10" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="T10" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="U10" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O10" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P10" s="2" t="inlineStr">
-        <is>
-          <t>0,49%</t>
-        </is>
-      </c>
-      <c r="Q10" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="R10" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S10" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T10" s="2" t="inlineStr">
-        <is>
-          <t>1959</t>
-        </is>
-      </c>
-      <c r="U10" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -1528,12 +1528,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>2811</t>
+          <t>2810</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>13081</t>
+          <t>13043</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1548,7 +1548,7 @@
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>5,24%</t>
+          <t>5,22%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1563,12 +1563,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>3000</t>
+          <t>3044</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>13945</t>
+          <t>15141</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1578,12 +1578,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>0,74%</t>
+          <t>0,75%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>3,45%</t>
+          <t>3,75%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1598,12 +1598,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>7704</t>
+          <t>7647</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>22030</t>
+          <t>23081</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1613,12 +1613,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>1,18%</t>
+          <t>1,17%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>3,37%</t>
+          <t>3,53%</t>
         </is>
       </c>
     </row>
@@ -1641,12 +1641,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>5746</t>
+          <t>5793</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>19421</t>
+          <t>20038</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1656,12 +1656,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>2,3%</t>
+          <t>2,32%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>7,77%</t>
+          <t>8,02%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1676,12 +1676,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>11287</t>
+          <t>11260</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>28675</t>
+          <t>28002</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1696,7 +1696,7 @@
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>7,1%</t>
+          <t>6,93%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1711,12 +1711,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>20174</t>
+          <t>20765</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>41034</t>
+          <t>42876</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1726,12 +1726,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>3,08%</t>
+          <t>3,18%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>6,27%</t>
+          <t>6,56%</t>
         </is>
       </c>
     </row>
@@ -1754,12 +1754,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>5215</t>
+          <t>4357</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>18591</t>
+          <t>17090</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1769,12 +1769,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>2,09%</t>
+          <t>1,74%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>7,44%</t>
+          <t>6,84%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1789,12 +1789,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>3057</t>
+          <t>3747</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>15021</t>
+          <t>15559</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1804,12 +1804,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>0,76%</t>
+          <t>0,93%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>3,72%</t>
+          <t>3,85%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1824,12 +1824,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>10647</t>
+          <t>10805</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>26678</t>
+          <t>26944</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1839,12 +1839,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>1,63%</t>
+          <t>1,65%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>4,08%</t>
+          <t>4,12%</t>
         </is>
       </c>
     </row>
@@ -1867,12 +1867,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>211208</t>
+          <t>210516</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>230950</t>
+          <t>231164</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1882,12 +1882,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>84,53%</t>
+          <t>84,26%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>92,43%</t>
+          <t>92,52%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1902,12 +1902,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>358909</t>
+          <t>358781</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>381303</t>
+          <t>380752</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1917,12 +1917,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>88,81%</t>
+          <t>88,77%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>94,35%</t>
+          <t>94,21%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1937,12 +1937,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>577111</t>
+          <t>575832</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>606720</t>
+          <t>606466</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1952,12 +1952,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>88,24%</t>
+          <t>88,05%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>92,77%</t>
+          <t>92,73%</t>
         </is>
       </c>
     </row>
@@ -2097,97 +2097,97 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>2051</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="K16" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>2,86%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
+      <c r="O16" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P16" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q16" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="K16" s="2" t="inlineStr">
+      <c r="R16" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>1988</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
+      <c r="S16" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="T16" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="U16" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O16" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P16" s="2" t="inlineStr">
-        <is>
-          <t>1,71%</t>
-        </is>
-      </c>
-      <c r="Q16" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="R16" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S16" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T16" s="2" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
-      </c>
-      <c r="U16" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>1,08%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -2215,7 +2215,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>7257</t>
+          <t>7423</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2230,7 +2230,7 @@
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>10,11%</t>
+          <t>10,34%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2250,7 +2250,7 @@
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>6141</t>
+          <t>6735</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2265,7 +2265,7 @@
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>5,29%</t>
+          <t>5,8%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2280,12 +2280,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1038</t>
+          <t>1003</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>9986</t>
+          <t>10548</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2295,12 +2295,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>0,55%</t>
+          <t>0,53%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>5,31%</t>
+          <t>5,61%</t>
         </is>
       </c>
     </row>
@@ -2323,12 +2323,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>6956</t>
+          <t>7075</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>21659</t>
+          <t>22159</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2338,12 +2338,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>9,69%</t>
+          <t>9,86%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>30,18%</t>
+          <t>30,88%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2358,12 +2358,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>4437</t>
+          <t>4161</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>16700</t>
+          <t>17389</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2373,12 +2373,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>3,82%</t>
+          <t>3,58%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>14,38%</t>
+          <t>14,97%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2393,12 +2393,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>13513</t>
+          <t>14032</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>32843</t>
+          <t>34224</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2408,12 +2408,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>7,19%</t>
+          <t>7,47%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>17,48%</t>
+          <t>18,21%</t>
         </is>
       </c>
     </row>
@@ -2436,12 +2436,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>2564</t>
+          <t>1927</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>11641</t>
+          <t>10842</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2451,12 +2451,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>3,57%</t>
+          <t>2,68%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>16,22%</t>
+          <t>15,11%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2471,12 +2471,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>5517</t>
+          <t>5367</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>19553</t>
+          <t>18662</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2486,12 +2486,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>4,75%</t>
+          <t>4,62%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>16,83%</t>
+          <t>16,07%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2506,12 +2506,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>9540</t>
+          <t>9393</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>25333</t>
+          <t>25312</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2521,12 +2521,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>5,08%</t>
+          <t>5,0%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>13,48%</t>
+          <t>13,47%</t>
         </is>
       </c>
     </row>
@@ -2549,12 +2549,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>42000</t>
+          <t>40861</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>57763</t>
+          <t>58100</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2564,12 +2564,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>58,52%</t>
+          <t>56,93%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>80,49%</t>
+          <t>80,95%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2584,12 +2584,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>84144</t>
+          <t>84060</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>101841</t>
+          <t>102740</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2599,12 +2599,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>72,45%</t>
+          <t>72,37%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>87,68%</t>
+          <t>88,46%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2619,12 +2619,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>132674</t>
+          <t>132664</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>157382</t>
+          <t>156188</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2639,7 +2639,7 @@
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>83,75%</t>
+          <t>83,12%</t>
         </is>
       </c>
     </row>
@@ -2779,97 +2779,97 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>1911</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
+      <c r="K22" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L22" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M22" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N22" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H22" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I22" s="2" t="inlineStr">
-        <is>
-          <t>0,29%</t>
-        </is>
-      </c>
-      <c r="J22" s="2" t="inlineStr">
+      <c r="O22" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P22" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q22" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="K22" s="2" t="inlineStr">
+      <c r="R22" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="L22" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M22" s="2" t="inlineStr">
-        <is>
-          <t>1968</t>
-        </is>
-      </c>
-      <c r="N22" s="2" t="inlineStr">
+      <c r="S22" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="T22" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="U22" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O22" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P22" s="2" t="inlineStr">
-        <is>
-          <t>0,19%</t>
-        </is>
-      </c>
-      <c r="Q22" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="R22" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S22" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T22" s="2" t="inlineStr">
-        <is>
-          <t>1947</t>
-        </is>
-      </c>
-      <c r="U22" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>0,11%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -2892,12 +2892,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>8678</t>
+          <t>8798</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>23376</t>
+          <t>23854</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2907,12 +2907,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>1,32%</t>
+          <t>1,34%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>3,56%</t>
+          <t>3,64%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2927,12 +2927,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>4896</t>
+          <t>4941</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>17971</t>
+          <t>17098</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2947,7 +2947,7 @@
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>1,71%</t>
+          <t>1,63%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2962,12 +2962,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>16490</t>
+          <t>17145</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>36763</t>
+          <t>36974</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2977,12 +2977,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>0,97%</t>
+          <t>1,01%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>2,16%</t>
+          <t>2,17%</t>
         </is>
       </c>
     </row>
@@ -3005,12 +3005,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>19288</t>
+          <t>20450</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>42364</t>
+          <t>42519</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3020,12 +3020,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>2,94%</t>
+          <t>3,12%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>6,46%</t>
+          <t>6,48%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3040,12 +3040,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>19326</t>
+          <t>19124</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>41841</t>
+          <t>41817</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3055,7 +3055,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>1,84%</t>
+          <t>1,82%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3075,12 +3075,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>44877</t>
+          <t>44864</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>77346</t>
+          <t>75896</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3095,7 +3095,7 @@
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>4,54%</t>
+          <t>4,45%</t>
         </is>
       </c>
     </row>
@@ -3118,12 +3118,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>10486</t>
+          <t>10375</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>26565</t>
+          <t>27078</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3133,12 +3133,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>1,6%</t>
+          <t>1,58%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>4,05%</t>
+          <t>4,13%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3153,12 +3153,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>16366</t>
+          <t>16555</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>37487</t>
+          <t>37560</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3168,7 +3168,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>1,56%</t>
+          <t>1,58%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3188,12 +3188,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>30349</t>
+          <t>32233</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>56208</t>
+          <t>58534</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3203,12 +3203,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>1,78%</t>
+          <t>1,89%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>3,3%</t>
+          <t>3,43%</t>
         </is>
       </c>
     </row>
@@ -3231,12 +3231,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>578628</t>
+          <t>576484</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>608216</t>
+          <t>607664</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3246,12 +3246,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>88,23%</t>
+          <t>87,9%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>92,74%</t>
+          <t>92,66%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3266,12 +3266,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>967160</t>
+          <t>964140</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>998057</t>
+          <t>997163</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3281,12 +3281,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>92,25%</t>
+          <t>91,97%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>95,2%</t>
+          <t>95,12%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3301,12 +3301,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1555133</t>
+          <t>1552659</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1600341</t>
+          <t>1598206</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3316,12 +3316,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>91,25%</t>
+          <t>91,11%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>93,91%</t>
+          <t>93,78%</t>
         </is>
       </c>
     </row>
@@ -3497,7 +3497,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según era el médico al que consultó en la última visita en 2012</t>
+          <t>Población según a dónde pertenecía el/a médico/a al que consultó en las últimas 2 semanas en 2012 (tasa de respuesta: 98,38%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -3697,7 +3697,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>4642</t>
+          <t>4593</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3712,7 +3712,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>1,38%</t>
+          <t>1,36%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3727,62 +3727,62 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="O4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q4" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R4" s="2" t="inlineStr">
+        <is>
+          <t>916</t>
+        </is>
+      </c>
+      <c r="S4" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>2033</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
+      <c r="T4" s="2" t="inlineStr">
+        <is>
+          <t>5327</t>
+        </is>
+      </c>
+      <c r="U4" s="2" t="inlineStr">
+        <is>
+          <t>0,1%</t>
+        </is>
+      </c>
+      <c r="V4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O4" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P4" s="2" t="inlineStr">
-        <is>
-          <t>0,38%</t>
-        </is>
-      </c>
-      <c r="Q4" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R4" s="2" t="inlineStr">
-        <is>
-          <t>916</t>
-        </is>
-      </c>
-      <c r="S4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T4" s="2" t="inlineStr">
-        <is>
-          <t>4284</t>
-        </is>
-      </c>
-      <c r="U4" s="2" t="inlineStr">
-        <is>
-          <t>0,1%</t>
-        </is>
-      </c>
-      <c r="V4" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>0,49%</t>
+          <t>0,61%</t>
         </is>
       </c>
     </row>
@@ -3805,12 +3805,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>945</t>
+          <t>937</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>10087</t>
+          <t>9659</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3825,7 +3825,7 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>2,99%</t>
+          <t>2,86%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -3845,7 +3845,7 @@
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>4806</t>
+          <t>4763</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -3860,7 +3860,7 @@
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>0,89%</t>
+          <t>0,88%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3875,12 +3875,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>989</t>
+          <t>962</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>10309</t>
+          <t>10410</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3895,7 +3895,7 @@
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>1,17%</t>
+          <t>1,18%</t>
         </is>
       </c>
     </row>
@@ -3918,12 +3918,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>1071</t>
+          <t>1097</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>9865</t>
+          <t>10638</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -3938,7 +3938,7 @@
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>2,92%</t>
+          <t>3,15%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -3953,12 +3953,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>3152</t>
+          <t>3162</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>15579</t>
+          <t>14950</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -3973,7 +3973,7 @@
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>2,88%</t>
+          <t>2,76%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -3988,12 +3988,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>6311</t>
+          <t>5996</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>20348</t>
+          <t>19770</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -4003,12 +4003,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>0,72%</t>
+          <t>0,68%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>2,32%</t>
+          <t>2,25%</t>
         </is>
       </c>
     </row>
@@ -4031,12 +4031,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>916</t>
+          <t>940</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>7893</t>
+          <t>7940</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4046,12 +4046,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,27%</t>
+          <t>0,28%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>2,34%</t>
+          <t>2,35%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4071,7 +4071,7 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>8287</t>
+          <t>8071</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4086,7 +4086,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>1,53%</t>
+          <t>1,49%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4101,12 +4101,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>2104</t>
+          <t>1990</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>12292</t>
+          <t>11952</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4116,12 +4116,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,24%</t>
+          <t>0,23%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>1,4%</t>
+          <t>1,36%</t>
         </is>
       </c>
     </row>
@@ -4144,12 +4144,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>317726</t>
+          <t>316881</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>331266</t>
+          <t>330932</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4159,12 +4159,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>94,15%</t>
+          <t>93,9%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>98,16%</t>
+          <t>98,06%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4179,12 +4179,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>521865</t>
+          <t>521620</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>535898</t>
+          <t>535222</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4194,12 +4194,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>96,43%</t>
+          <t>96,39%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>99,02%</t>
+          <t>98,9%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4214,12 +4214,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>844728</t>
+          <t>844723</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>863464</t>
+          <t>864161</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4234,7 +4234,7 @@
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>98,27%</t>
+          <t>98,35%</t>
         </is>
       </c>
     </row>
@@ -4374,97 +4374,97 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>2056</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>0,58%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
+      <c r="O10" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P10" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q10" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="K10" s="2" t="inlineStr">
+      <c r="R10" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>2048</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
+      <c r="S10" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="T10" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="U10" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O10" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P10" s="2" t="inlineStr">
-        <is>
-          <t>0,42%</t>
-        </is>
-      </c>
-      <c r="Q10" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="R10" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S10" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T10" s="2" t="inlineStr">
-        <is>
-          <t>2055</t>
-        </is>
-      </c>
-      <c r="U10" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>0,24%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -4487,12 +4487,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>790</t>
+          <t>785</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>7504</t>
+          <t>7410</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4507,7 +4507,7 @@
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>2,11%</t>
+          <t>2,08%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4522,12 +4522,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>2048</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4537,12 +4537,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>0,42%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4557,12 +4557,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>801</t>
+          <t>804</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>8043</t>
+          <t>7144</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4577,7 +4577,7 @@
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>0,96%</t>
+          <t>0,85%</t>
         </is>
       </c>
     </row>
@@ -4600,12 +4600,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>3783</t>
+          <t>3807</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>14800</t>
+          <t>14542</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -4615,12 +4615,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>1,06%</t>
+          <t>1,07%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>4,16%</t>
+          <t>4,09%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -4635,12 +4635,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>3963</t>
+          <t>4846</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>16648</t>
+          <t>17053</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -4650,12 +4650,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>0,81%</t>
+          <t>1,0%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>3,42%</t>
+          <t>3,5%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -4670,12 +4670,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>9927</t>
+          <t>9871</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>26644</t>
+          <t>25963</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -4685,12 +4685,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>1,18%</t>
+          <t>1,17%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>3,16%</t>
+          <t>3,08%</t>
         </is>
       </c>
     </row>
@@ -4713,12 +4713,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>9644</t>
+          <t>8750</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>30068</t>
+          <t>28686</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4728,12 +4728,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>2,71%</t>
+          <t>2,46%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>8,46%</t>
+          <t>8,07%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -4748,12 +4748,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>1206</t>
+          <t>1115</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>13193</t>
+          <t>12326</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -4763,12 +4763,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>0,25%</t>
+          <t>0,23%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>2,71%</t>
+          <t>2,53%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4783,12 +4783,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>12409</t>
+          <t>12604</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>34939</t>
+          <t>34012</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4798,12 +4798,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>1,47%</t>
+          <t>1,5%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>4,15%</t>
+          <t>4,04%</t>
         </is>
       </c>
     </row>
@@ -4826,12 +4826,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>313696</t>
+          <t>316121</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>337132</t>
+          <t>338139</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4841,12 +4841,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>88,23%</t>
+          <t>88,92%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>94,83%</t>
+          <t>95,11%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4861,12 +4861,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>462597</t>
+          <t>463256</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>478707</t>
+          <t>478594</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4876,12 +4876,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>95,08%</t>
+          <t>95,21%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>98,39%</t>
+          <t>98,36%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -4896,12 +4896,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>786123</t>
+          <t>785971</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>813291</t>
+          <t>813242</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4911,7 +4911,7 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>93,36%</t>
+          <t>93,34%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
@@ -5056,97 +5056,97 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>2170</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="K16" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>2,9%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
+      <c r="O16" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P16" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q16" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="K16" s="2" t="inlineStr">
+      <c r="R16" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>2220</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
+      <c r="S16" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="T16" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="U16" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O16" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P16" s="2" t="inlineStr">
-        <is>
-          <t>2,06%</t>
-        </is>
-      </c>
-      <c r="Q16" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="R16" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S16" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T16" s="2" t="inlineStr">
-        <is>
-          <t>2216</t>
-        </is>
-      </c>
-      <c r="U16" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>1,21%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -5174,7 +5174,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>6057</t>
+          <t>4585</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5189,7 +5189,7 @@
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>8,1%</t>
+          <t>6,13%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5209,7 +5209,7 @@
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>7409</t>
+          <t>8892</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5224,7 +5224,7 @@
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>6,88%</t>
+          <t>8,25%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5244,7 +5244,7 @@
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>9091</t>
+          <t>9595</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5259,7 +5259,7 @@
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>4,98%</t>
+          <t>5,26%</t>
         </is>
       </c>
     </row>
@@ -5282,12 +5282,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>2802</t>
+          <t>2988</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>15231</t>
+          <t>15613</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -5297,12 +5297,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>3,75%</t>
+          <t>3,99%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>20,36%</t>
+          <t>20,87%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -5317,12 +5317,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>900</t>
+          <t>880</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>7914</t>
+          <t>7693</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -5332,12 +5332,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>0,84%</t>
+          <t>0,82%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>7,35%</t>
+          <t>7,14%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -5352,12 +5352,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>4837</t>
+          <t>4883</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>19087</t>
+          <t>20418</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -5367,12 +5367,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>2,65%</t>
+          <t>2,67%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>10,46%</t>
+          <t>11,18%</t>
         </is>
       </c>
     </row>
@@ -5395,12 +5395,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>1927</t>
+          <t>2009</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>11081</t>
+          <t>10935</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5410,12 +5410,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>2,58%</t>
+          <t>2,68%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>14,81%</t>
+          <t>14,62%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5430,12 +5430,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>9387</t>
+          <t>9249</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>26413</t>
+          <t>27019</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5445,12 +5445,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>8,71%</t>
+          <t>8,59%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>24,52%</t>
+          <t>25,08%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5465,12 +5465,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>13387</t>
+          <t>13667</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>33316</t>
+          <t>32919</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5480,12 +5480,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>7,33%</t>
+          <t>7,49%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>18,25%</t>
+          <t>18,03%</t>
         </is>
       </c>
     </row>
@@ -5508,12 +5508,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>53755</t>
+          <t>52814</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>67464</t>
+          <t>67515</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5523,12 +5523,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>71,85%</t>
+          <t>70,59%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>90,17%</t>
+          <t>90,24%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5543,12 +5543,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>76653</t>
+          <t>76347</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>95393</t>
+          <t>94203</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5558,12 +5558,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>71,15%</t>
+          <t>70,87%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>88,55%</t>
+          <t>87,44%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5578,12 +5578,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>135892</t>
+          <t>134153</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>158926</t>
+          <t>157551</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5593,12 +5593,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>74,44%</t>
+          <t>73,49%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>87,06%</t>
+          <t>86,31%</t>
         </is>
       </c>
     </row>
@@ -5743,7 +5743,7 @@
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>4666</t>
+          <t>5154</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5758,7 +5758,7 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>0,61%</t>
+          <t>0,67%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5773,62 +5773,62 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M22" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N22" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="O22" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P22" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q22" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R22" s="2" t="inlineStr">
+        <is>
+          <t>916</t>
+        </is>
+      </c>
+      <c r="S22" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M22" s="2" t="inlineStr">
-        <is>
-          <t>2061</t>
-        </is>
-      </c>
-      <c r="N22" s="2" t="inlineStr">
+      <c r="T22" s="2" t="inlineStr">
+        <is>
+          <t>4601</t>
+        </is>
+      </c>
+      <c r="U22" s="2" t="inlineStr">
+        <is>
+          <t>0,05%</t>
+        </is>
+      </c>
+      <c r="V22" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O22" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P22" s="2" t="inlineStr">
-        <is>
-          <t>0,18%</t>
-        </is>
-      </c>
-      <c r="Q22" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R22" s="2" t="inlineStr">
-        <is>
-          <t>916</t>
-        </is>
-      </c>
-      <c r="S22" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T22" s="2" t="inlineStr">
-        <is>
-          <t>6057</t>
-        </is>
-      </c>
-      <c r="U22" s="2" t="inlineStr">
-        <is>
-          <t>0,05%</t>
-        </is>
-      </c>
-      <c r="V22" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>0,32%</t>
+          <t>0,24%</t>
         </is>
       </c>
     </row>
@@ -5851,12 +5851,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>2929</t>
+          <t>2919</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>14125</t>
+          <t>14723</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -5871,7 +5871,7 @@
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>1,84%</t>
+          <t>1,92%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -5891,7 +5891,7 @@
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>9094</t>
+          <t>9882</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -5906,7 +5906,7 @@
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>0,87%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -5921,12 +5921,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>4680</t>
+          <t>4760</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>19053</t>
+          <t>18865</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -5941,7 +5941,7 @@
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>1,0%</t>
+          <t>0,99%</t>
         </is>
       </c>
     </row>
@@ -5964,12 +5964,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>11510</t>
+          <t>11233</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>31423</t>
+          <t>30481</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -5979,12 +5979,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>1,5%</t>
+          <t>1,46%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>4,09%</t>
+          <t>3,97%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -5999,12 +5999,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>11598</t>
+          <t>11936</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>28378</t>
+          <t>30354</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -6014,12 +6014,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>1,02%</t>
+          <t>1,05%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>2,5%</t>
+          <t>2,67%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -6034,12 +6034,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>27016</t>
+          <t>27673</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>51501</t>
+          <t>52400</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -6049,12 +6049,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>1,42%</t>
+          <t>1,45%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>2,71%</t>
+          <t>2,75%</t>
         </is>
       </c>
     </row>
@@ -6077,12 +6077,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>14933</t>
+          <t>15205</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>37148</t>
+          <t>38537</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6092,12 +6092,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>1,94%</t>
+          <t>1,98%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>4,84%</t>
+          <t>5,02%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6112,12 +6112,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>15047</t>
+          <t>14718</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>36253</t>
+          <t>37116</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6127,12 +6127,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>1,33%</t>
+          <t>1,3%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>3,19%</t>
+          <t>3,27%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6147,12 +6147,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>35073</t>
+          <t>35345</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>66699</t>
+          <t>67153</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6162,12 +6162,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>1,84%</t>
+          <t>1,86%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>3,5%</t>
+          <t>3,53%</t>
         </is>
       </c>
     </row>
@@ -6190,12 +6190,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>700590</t>
+          <t>699275</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>730559</t>
+          <t>729420</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6205,12 +6205,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>91,24%</t>
+          <t>91,07%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>95,15%</t>
+          <t>95,0%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6225,12 +6225,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>1073478</t>
+          <t>1073072</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>1101905</t>
+          <t>1101984</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6240,12 +6240,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>94,54%</t>
+          <t>94,5%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>97,04%</t>
+          <t>97,05%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6260,12 +6260,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1782806</t>
+          <t>1782153</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1825525</t>
+          <t>1825030</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6275,12 +6275,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>93,67%</t>
+          <t>93,64%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>95,91%</t>
+          <t>95,89%</t>
         </is>
       </c>
     </row>
@@ -6456,7 +6456,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según era el médico al que consultó en la última visita en 2016</t>
+          <t>Población según a dónde pertenecía el/a médico/a al que consultó en las últimas 2 semanas en 2016 (tasa de respuesta: 98,31%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -6651,97 +6651,97 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>1885</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>0,73%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
+      <c r="O4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q4" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="K4" s="2" t="inlineStr">
+      <c r="R4" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>2145</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
+      <c r="S4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="T4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="U4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O4" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P4" s="2" t="inlineStr">
-        <is>
-          <t>0,52%</t>
-        </is>
-      </c>
-      <c r="Q4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="R4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T4" s="2" t="inlineStr">
-        <is>
-          <t>2041</t>
-        </is>
-      </c>
-      <c r="U4" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -6764,97 +6764,97 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>1949</t>
+        </is>
+      </c>
+      <c r="L5" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>1885</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>6614</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
+        <is>
+          <t>0,47%</t>
+        </is>
+      </c>
+      <c r="O5" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>0,73%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
+      <c r="P5" s="2" t="inlineStr">
+        <is>
+          <t>1,61%</t>
+        </is>
+      </c>
+      <c r="Q5" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="K5" s="2" t="inlineStr">
+      <c r="R5" s="2" t="inlineStr">
         <is>
           <t>1949</t>
         </is>
       </c>
-      <c r="L5" s="2" t="inlineStr">
+      <c r="S5" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>6599</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>0,47%</t>
-        </is>
-      </c>
-      <c r="O5" s="2" t="inlineStr">
+      <c r="T5" s="2" t="inlineStr">
+        <is>
+          <t>7045</t>
+        </is>
+      </c>
+      <c r="U5" s="2" t="inlineStr">
+        <is>
+          <t>0,29%</t>
+        </is>
+      </c>
+      <c r="V5" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P5" s="2" t="inlineStr">
-        <is>
-          <t>1,6%</t>
-        </is>
-      </c>
-      <c r="Q5" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="R5" s="2" t="inlineStr">
-        <is>
-          <t>1949</t>
-        </is>
-      </c>
-      <c r="S5" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T5" s="2" t="inlineStr">
-        <is>
-          <t>6641</t>
-        </is>
-      </c>
-      <c r="U5" s="2" t="inlineStr">
-        <is>
-          <t>0,29%</t>
-        </is>
-      </c>
-      <c r="V5" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>0,99%</t>
+          <t>1,05%</t>
         </is>
       </c>
     </row>
@@ -6877,12 +6877,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>1885</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -6892,12 +6892,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>0,73%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -6912,12 +6912,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>1133</t>
+          <t>1135</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>11269</t>
+          <t>12247</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -6932,7 +6932,7 @@
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>2,74%</t>
+          <t>2,98%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -6952,7 +6952,7 @@
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>11929</t>
+          <t>12440</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -6967,7 +6967,7 @@
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>1,78%</t>
+          <t>1,86%</t>
         </is>
       </c>
     </row>
@@ -6990,12 +6990,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>2037</t>
+          <t>2051</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>11362</t>
+          <t>11678</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -7010,7 +7010,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>4,4%</t>
+          <t>4,52%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -7025,12 +7025,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>3297</t>
+          <t>3339</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>15942</t>
+          <t>14987</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -7040,12 +7040,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>0,81%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>3,88%</t>
+          <t>3,64%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -7060,12 +7060,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>6873</t>
+          <t>7147</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>22952</t>
+          <t>22354</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7075,12 +7075,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>1,03%</t>
+          <t>1,07%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>3,43%</t>
+          <t>3,34%</t>
         </is>
       </c>
     </row>
@@ -7103,12 +7103,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>246902</t>
+          <t>246586</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>256227</t>
+          <t>256213</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -7118,7 +7118,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>95,6%</t>
+          <t>95,48%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -7138,12 +7138,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>388122</t>
+          <t>387863</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>403989</t>
+          <t>404269</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -7153,12 +7153,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>94,37%</t>
+          <t>94,31%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>98,23%</t>
+          <t>98,3%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7173,12 +7173,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>639179</t>
+          <t>640013</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>658072</t>
+          <t>657805</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -7188,12 +7188,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>95,47%</t>
+          <t>95,59%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>98,29%</t>
+          <t>98,25%</t>
         </is>
       </c>
     </row>
@@ -7338,7 +7338,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>4843</t>
+          <t>5728</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -7353,7 +7353,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>1,05%</t>
+          <t>1,24%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -7368,47 +7368,47 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="O10" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P10" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q10" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R10" s="2" t="inlineStr">
+        <is>
+          <t>983</t>
+        </is>
+      </c>
+      <c r="S10" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>2029</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="O10" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P10" s="2" t="inlineStr">
-        <is>
-          <t>0,35%</t>
-        </is>
-      </c>
-      <c r="Q10" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R10" s="2" t="inlineStr">
-        <is>
-          <t>983</t>
-        </is>
-      </c>
-      <c r="S10" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>4906</t>
+          <t>4950</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -7446,12 +7446,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>3773</t>
+          <t>3838</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>15318</t>
+          <t>14859</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -7461,12 +7461,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>0,82%</t>
+          <t>0,83%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>3,33%</t>
+          <t>3,23%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -7486,7 +7486,7 @@
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>6865</t>
+          <t>7143</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -7501,7 +7501,7 @@
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>1,17%</t>
+          <t>1,22%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -7516,12 +7516,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>4996</t>
+          <t>4849</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>17538</t>
+          <t>17552</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -7531,7 +7531,7 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>0,48%</t>
+          <t>0,46%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -7559,12 +7559,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>4602</t>
+          <t>4323</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>17355</t>
+          <t>18346</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -7574,12 +7574,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>1,0%</t>
+          <t>0,94%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>3,77%</t>
+          <t>3,98%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -7594,12 +7594,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>5458</t>
+          <t>5420</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>19705</t>
+          <t>20581</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -7614,7 +7614,7 @@
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>3,37%</t>
+          <t>3,52%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -7629,12 +7629,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>13005</t>
+          <t>12335</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>31959</t>
+          <t>30844</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -7644,12 +7644,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>1,24%</t>
+          <t>1,18%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>3,06%</t>
+          <t>2,95%</t>
         </is>
       </c>
     </row>
@@ -7672,12 +7672,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>15912</t>
+          <t>14875</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>36375</t>
+          <t>35656</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -7687,12 +7687,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>3,45%</t>
+          <t>3,23%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>7,9%</t>
+          <t>7,74%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7707,12 +7707,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>12078</t>
+          <t>11665</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>32426</t>
+          <t>29513</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -7722,12 +7722,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>2,07%</t>
+          <t>2,0%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>5,55%</t>
+          <t>5,05%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7742,12 +7742,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>31239</t>
+          <t>31396</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>60022</t>
+          <t>59220</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -7757,12 +7757,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>2,99%</t>
+          <t>3,0%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>5,74%</t>
+          <t>5,67%</t>
         </is>
       </c>
     </row>
@@ -7785,12 +7785,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>404915</t>
+          <t>402754</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>429496</t>
+          <t>429659</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -7800,12 +7800,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>87,9%</t>
+          <t>87,43%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>93,23%</t>
+          <t>93,27%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7820,12 +7820,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>538303</t>
+          <t>538828</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>562392</t>
+          <t>561594</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -7835,12 +7835,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>92,13%</t>
+          <t>92,22%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>96,25%</t>
+          <t>96,12%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7855,12 +7855,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>952660</t>
+          <t>951969</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>987022</t>
+          <t>987510</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -7870,12 +7870,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>91,17%</t>
+          <t>91,1%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>94,46%</t>
+          <t>94,5%</t>
         </is>
       </c>
     </row>
@@ -8015,97 +8015,97 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>2104</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="K16" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>1,74%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
+      <c r="O16" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P16" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q16" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="K16" s="2" t="inlineStr">
+      <c r="R16" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>2029</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
+      <c r="S16" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="T16" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="U16" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O16" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P16" s="2" t="inlineStr">
-        <is>
-          <t>1,46%</t>
-        </is>
-      </c>
-      <c r="Q16" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="R16" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S16" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T16" s="2" t="inlineStr">
-        <is>
-          <t>2074</t>
-        </is>
-      </c>
-      <c r="U16" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -8128,12 +8128,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>968</t>
+          <t>966</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>8480</t>
+          <t>8450</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -8148,7 +8148,7 @@
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>7,03%</t>
+          <t>7,0%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8168,7 +8168,7 @@
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>4560</t>
+          <t>3621</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -8183,7 +8183,7 @@
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>3,29%</t>
+          <t>2,61%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8198,12 +8198,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>994</t>
+          <t>1132</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>10079</t>
+          <t>10166</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8213,12 +8213,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>0,38%</t>
+          <t>0,44%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>3,89%</t>
+          <t>3,92%</t>
         </is>
       </c>
     </row>
@@ -8241,12 +8241,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>2660</t>
+          <t>2709</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>14384</t>
+          <t>13518</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -8256,12 +8256,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>2,2%</t>
+          <t>2,24%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>11,92%</t>
+          <t>11,2%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -8276,12 +8276,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>1008</t>
+          <t>1064</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>9760</t>
+          <t>9375</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -8291,12 +8291,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>0,73%</t>
+          <t>0,77%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>7,04%</t>
+          <t>6,76%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -8311,12 +8311,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>5298</t>
+          <t>5784</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>19436</t>
+          <t>20865</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -8326,12 +8326,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>2,04%</t>
+          <t>2,23%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>7,49%</t>
+          <t>8,05%</t>
         </is>
       </c>
     </row>
@@ -8354,12 +8354,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>8885</t>
+          <t>8974</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>24745</t>
+          <t>24918</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -8369,12 +8369,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>7,36%</t>
+          <t>7,43%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>20,5%</t>
+          <t>20,64%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -8389,12 +8389,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>12028</t>
+          <t>11563</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>29373</t>
+          <t>28815</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -8404,12 +8404,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>8,68%</t>
+          <t>8,34%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>21,19%</t>
+          <t>20,79%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -8424,12 +8424,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>25220</t>
+          <t>25240</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>48137</t>
+          <t>48514</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -8444,7 +8444,7 @@
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>18,56%</t>
+          <t>18,71%</t>
         </is>
       </c>
     </row>
@@ -8467,12 +8467,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>84024</t>
+          <t>85274</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>104353</t>
+          <t>104665</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -8482,12 +8482,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>69,61%</t>
+          <t>70,65%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>86,45%</t>
+          <t>86,71%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -8502,12 +8502,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>103132</t>
+          <t>103646</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>122452</t>
+          <t>122820</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -8517,12 +8517,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>74,4%</t>
+          <t>74,77%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>88,33%</t>
+          <t>88,6%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -8537,12 +8537,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>195394</t>
+          <t>194047</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>221820</t>
+          <t>221226</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -8552,12 +8552,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>75,35%</t>
+          <t>74,83%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>85,54%</t>
+          <t>85,31%</t>
         </is>
       </c>
     </row>
@@ -8702,7 +8702,7 @@
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>5509</t>
+          <t>6438</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -8717,7 +8717,7 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>0,66%</t>
+          <t>0,77%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -8732,62 +8732,62 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M22" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N22" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="O22" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P22" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q22" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R22" s="2" t="inlineStr">
+        <is>
+          <t>983</t>
+        </is>
+      </c>
+      <c r="S22" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M22" s="2" t="inlineStr">
-        <is>
-          <t>2074</t>
-        </is>
-      </c>
-      <c r="N22" s="2" t="inlineStr">
+      <c r="T22" s="2" t="inlineStr">
+        <is>
+          <t>5665</t>
+        </is>
+      </c>
+      <c r="U22" s="2" t="inlineStr">
+        <is>
+          <t>0,05%</t>
+        </is>
+      </c>
+      <c r="V22" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O22" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P22" s="2" t="inlineStr">
-        <is>
-          <t>0,18%</t>
-        </is>
-      </c>
-      <c r="Q22" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R22" s="2" t="inlineStr">
-        <is>
-          <t>983</t>
-        </is>
-      </c>
-      <c r="S22" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T22" s="2" t="inlineStr">
-        <is>
-          <t>4652</t>
-        </is>
-      </c>
-      <c r="U22" s="2" t="inlineStr">
-        <is>
-          <t>0,05%</t>
-        </is>
-      </c>
-      <c r="V22" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>0,24%</t>
+          <t>0,29%</t>
         </is>
       </c>
     </row>
@@ -8810,12 +8810,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>5888</t>
+          <t>5898</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>19710</t>
+          <t>18867</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -8830,7 +8830,7 @@
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>2,35%</t>
+          <t>2,25%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -8845,12 +8845,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>1784</t>
+          <t>1763</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>11421</t>
+          <t>10630</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -8865,7 +8865,7 @@
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>1,01%</t>
+          <t>0,94%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -8880,12 +8880,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>9453</t>
+          <t>9748</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>24871</t>
+          <t>24831</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -8895,7 +8895,7 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>0,48%</t>
+          <t>0,49%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
@@ -8923,12 +8923,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>9444</t>
+          <t>8771</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>26807</t>
+          <t>26341</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -8938,12 +8938,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>1,12%</t>
+          <t>1,04%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>3,19%</t>
+          <t>3,14%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -8958,12 +8958,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>11743</t>
+          <t>11609</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>30609</t>
+          <t>30120</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -8973,12 +8973,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>1,04%</t>
+          <t>1,02%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>2,7%</t>
+          <t>2,66%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -8993,12 +8993,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>24135</t>
+          <t>24582</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>49296</t>
+          <t>50426</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -9008,12 +9008,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>1,22%</t>
+          <t>1,25%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>2,5%</t>
+          <t>2,55%</t>
         </is>
       </c>
     </row>
@@ -9036,12 +9036,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>31185</t>
+          <t>32695</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>60009</t>
+          <t>60268</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -9051,12 +9051,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>3,71%</t>
+          <t>3,89%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>7,15%</t>
+          <t>7,18%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -9071,12 +9071,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>32338</t>
+          <t>33405</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>59844</t>
+          <t>61928</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -9086,12 +9086,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>2,85%</t>
+          <t>2,95%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>5,28%</t>
+          <t>5,46%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -9106,12 +9106,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>74487</t>
+          <t>72926</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>114536</t>
+          <t>112922</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -9121,12 +9121,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>3,77%</t>
+          <t>3,69%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>5,8%</t>
+          <t>5,72%</t>
         </is>
       </c>
     </row>
@@ -9149,12 +9149,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>748135</t>
+          <t>748469</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>782950</t>
+          <t>782572</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -9164,12 +9164,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>89,1%</t>
+          <t>89,14%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>93,25%</t>
+          <t>93,2%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -9184,12 +9184,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>1047311</t>
+          <t>1045157</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>1080758</t>
+          <t>1078616</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -9199,12 +9199,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>92,34%</t>
+          <t>92,15%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>95,29%</t>
+          <t>95,1%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -9219,12 +9219,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1805211</t>
+          <t>1802101</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1851872</t>
+          <t>1851859</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -9234,7 +9234,7 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>91,46%</t>
+          <t>91,3%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
@@ -9415,7 +9415,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según era el médico al que consultó en la última visita en 2023</t>
+          <t>Población según a dónde pertenecía el/a médico/a al que consultó en las últimas 2 semanas en 2023 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -9610,97 +9610,97 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>1403</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>1,02%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
+      <c r="O4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q4" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="K4" s="2" t="inlineStr">
+      <c r="R4" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>1032</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
+      <c r="S4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="T4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="U4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O4" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P4" s="2" t="inlineStr">
-        <is>
-          <t>0,43%</t>
-        </is>
-      </c>
-      <c r="Q4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="R4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T4" s="2" t="inlineStr">
-        <is>
-          <t>1145</t>
-        </is>
-      </c>
-      <c r="U4" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>0,31%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -9723,97 +9723,97 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>1403</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>1,02%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
+      <c r="O5" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P5" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q5" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="K5" s="2" t="inlineStr">
+      <c r="R5" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>1032</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
+      <c r="S5" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="T5" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="U5" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O5" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P5" s="2" t="inlineStr">
-        <is>
-          <t>0,43%</t>
-        </is>
-      </c>
-      <c r="Q5" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="R5" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S5" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T5" s="2" t="inlineStr">
-        <is>
-          <t>1145</t>
-        </is>
-      </c>
-      <c r="U5" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>0,31%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -9841,7 +9841,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>2055</t>
+          <t>2216</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -9856,7 +9856,7 @@
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>1,49%</t>
+          <t>1,61%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -9871,12 +9871,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>1128</t>
+          <t>1017</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>5941</t>
+          <t>6096</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -9886,12 +9886,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>0,47%</t>
+          <t>0,43%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>2,5%</t>
+          <t>2,57%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -9906,12 +9906,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>1513</t>
+          <t>1430</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>6515</t>
+          <t>6916</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -9921,12 +9921,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,38%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>1,74%</t>
+          <t>1,84%</t>
         </is>
       </c>
     </row>
@@ -9954,7 +9954,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>4491</t>
+          <t>5231</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -9969,7 +9969,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>3,27%</t>
+          <t>3,8%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -9984,12 +9984,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>875</t>
+          <t>552</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>7310</t>
+          <t>6424</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -9999,12 +9999,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>0,37%</t>
+          <t>0,23%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>3,08%</t>
+          <t>2,7%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -10019,12 +10019,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>1545</t>
+          <t>1570</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>8329</t>
+          <t>8731</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -10034,12 +10034,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,41%</t>
+          <t>0,42%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>2,22%</t>
+          <t>2,33%</t>
         </is>
       </c>
     </row>
@@ -10057,17 +10057,17 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>135583</t>
+          <t>135582</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>132384</t>
+          <t>132311</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>137082</t>
+          <t>137057</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -10077,12 +10077,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>96,27%</t>
+          <t>96,22%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>99,69%</t>
+          <t>99,67%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -10097,12 +10097,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>227642</t>
+          <t>227733</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>234908</t>
+          <t>234790</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -10112,12 +10112,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>95,81%</t>
+          <t>95,85%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>98,87%</t>
+          <t>98,82%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -10132,12 +10132,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>362306</t>
+          <t>362201</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>371212</t>
+          <t>371072</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -10147,12 +10147,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>96,59%</t>
+          <t>96,56%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>98,96%</t>
+          <t>98,92%</t>
         </is>
       </c>
     </row>
@@ -10170,17 +10170,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>137512</t>
+          <t>137511</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>137512</t>
+          <t>137511</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>137512</t>
+          <t>137511</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -10292,97 +10292,97 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>1342</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>1867</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>4792</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
+        <is>
+          <t>0,27%</t>
+        </is>
+      </c>
+      <c r="O10" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
+      <c r="P10" s="2" t="inlineStr">
+        <is>
+          <t>0,95%</t>
+        </is>
+      </c>
+      <c r="Q10" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="R10" s="2" t="inlineStr">
+        <is>
+          <t>1342</t>
+        </is>
+      </c>
+      <c r="S10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T10" s="2" t="inlineStr">
+        <is>
+          <t>4434</t>
+        </is>
+      </c>
+      <c r="U10" s="2" t="inlineStr">
+        <is>
+          <t>0,15%</t>
+        </is>
+      </c>
+      <c r="V10" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="W10" s="2" t="inlineStr">
         <is>
           <t>0,51%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>1342</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>4641</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>0,27%</t>
-        </is>
-      </c>
-      <c r="O10" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="P10" s="2" t="inlineStr">
-        <is>
-          <t>0,92%</t>
-        </is>
-      </c>
-      <c r="Q10" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="R10" s="2" t="inlineStr">
-        <is>
-          <t>1342</t>
-        </is>
-      </c>
-      <c r="S10" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T10" s="2" t="inlineStr">
-        <is>
-          <t>4296</t>
-        </is>
-      </c>
-      <c r="U10" s="2" t="inlineStr">
-        <is>
-          <t>0,15%</t>
-        </is>
-      </c>
-      <c r="V10" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="W10" s="2" t="inlineStr">
-        <is>
-          <t>0,49%</t>
         </is>
       </c>
     </row>
@@ -10405,12 +10405,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>1288</t>
+          <t>1244</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>10688</t>
+          <t>10240</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -10420,12 +10420,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>0,35%</t>
+          <t>0,34%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>2,89%</t>
+          <t>2,77%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -10440,12 +10440,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>1566</t>
+          <t>1717</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>10123</t>
+          <t>9672</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -10455,12 +10455,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>0,31%</t>
+          <t>0,34%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>2,02%</t>
+          <t>1,93%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -10475,12 +10475,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>4532</t>
+          <t>4555</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>17060</t>
+          <t>16898</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -10495,7 +10495,7 @@
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>1,96%</t>
+          <t>1,94%</t>
         </is>
       </c>
     </row>
@@ -10518,12 +10518,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>9014</t>
+          <t>8865</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>30969</t>
+          <t>31600</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -10533,12 +10533,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>2,44%</t>
+          <t>2,4%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>8,38%</t>
+          <t>8,55%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -10553,12 +10553,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>10345</t>
+          <t>10321</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>29213</t>
+          <t>28257</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -10568,12 +10568,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>2,06%</t>
+          <t>2,05%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>5,82%</t>
+          <t>5,63%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -10588,12 +10588,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>24176</t>
+          <t>23618</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>51680</t>
+          <t>51502</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -10603,12 +10603,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>2,77%</t>
+          <t>2,71%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>5,93%</t>
+          <t>5,91%</t>
         </is>
       </c>
     </row>
@@ -10631,12 +10631,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>7546</t>
+          <t>8265</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>23437</t>
+          <t>23711</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -10646,12 +10646,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>2,04%</t>
+          <t>2,24%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>6,34%</t>
+          <t>6,41%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -10666,12 +10666,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>9039</t>
+          <t>8625</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>24507</t>
+          <t>23728</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -10681,12 +10681,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>1,8%</t>
+          <t>1,72%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>4,88%</t>
+          <t>4,72%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -10701,12 +10701,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>20269</t>
+          <t>19893</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>41343</t>
+          <t>40986</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -10716,12 +10716,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>2,32%</t>
+          <t>2,28%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>4,74%</t>
+          <t>4,7%</t>
         </is>
       </c>
     </row>
@@ -10744,12 +10744,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>318703</t>
+          <t>319036</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>344994</t>
+          <t>345029</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -10759,12 +10759,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>86,22%</t>
+          <t>86,31%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>93,33%</t>
+          <t>93,34%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -10779,12 +10779,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>447510</t>
+          <t>449076</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>477274</t>
+          <t>479076</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -10794,12 +10794,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>89,09%</t>
+          <t>89,4%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>95,01%</t>
+          <t>95,37%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -10814,12 +10814,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>778094</t>
+          <t>777172</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>815873</t>
+          <t>817127</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -10829,12 +10829,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>89,23%</t>
+          <t>89,13%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>93,56%</t>
+          <t>93,71%</t>
         </is>
       </c>
     </row>
@@ -10974,97 +10974,97 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>1754</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="K16" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>1,31%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
+      <c r="O16" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P16" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q16" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="K16" s="2" t="inlineStr">
+      <c r="R16" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>1232</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
+      <c r="S16" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="T16" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="U16" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O16" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P16" s="2" t="inlineStr">
-        <is>
-          <t>0,8%</t>
-        </is>
-      </c>
-      <c r="Q16" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="R16" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S16" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T16" s="2" t="inlineStr">
-        <is>
-          <t>1434</t>
-        </is>
-      </c>
-      <c r="U16" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -11087,12 +11087,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>581</t>
+          <t>598</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>6109</t>
+          <t>5939</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -11102,12 +11102,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>0,44%</t>
+          <t>0,45%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>4,58%</t>
+          <t>4,45%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -11122,12 +11122,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>584</t>
+          <t>627</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>5747</t>
+          <t>5408</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -11137,12 +11137,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>0,38%</t>
+          <t>0,41%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>3,75%</t>
+          <t>3,52%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -11157,12 +11157,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1752</t>
+          <t>1787</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>9106</t>
+          <t>9288</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -11172,12 +11172,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>0,61%</t>
+          <t>0,62%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>3,17%</t>
+          <t>3,24%</t>
         </is>
       </c>
     </row>
@@ -11200,12 +11200,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>8734</t>
+          <t>8030</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>25363</t>
+          <t>23945</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -11215,12 +11215,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>6,54%</t>
+          <t>6,02%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>19,0%</t>
+          <t>17,94%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -11235,12 +11235,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>16337</t>
+          <t>16388</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>31999</t>
+          <t>32990</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -11250,12 +11250,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>10,65%</t>
+          <t>10,68%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>20,85%</t>
+          <t>21,5%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -11270,12 +11270,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>28563</t>
+          <t>28215</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>50721</t>
+          <t>51233</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -11285,12 +11285,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>9,95%</t>
+          <t>9,83%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>17,68%</t>
+          <t>17,86%</t>
         </is>
       </c>
     </row>
@@ -11313,12 +11313,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>5621</t>
+          <t>6108</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>19081</t>
+          <t>20013</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -11328,12 +11328,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>4,21%</t>
+          <t>4,58%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>14,29%</t>
+          <t>14,99%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -11348,12 +11348,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>10678</t>
+          <t>10378</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>23156</t>
+          <t>23029</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -11363,12 +11363,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>6,96%</t>
+          <t>6,76%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>15,09%</t>
+          <t>15,01%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -11383,12 +11383,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>18925</t>
+          <t>20019</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>37416</t>
+          <t>37977</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -11398,12 +11398,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>6,6%</t>
+          <t>6,98%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>13,04%</t>
+          <t>13,24%</t>
         </is>
       </c>
     </row>
@@ -11426,12 +11426,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>94288</t>
+          <t>93810</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>114019</t>
+          <t>113136</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -11441,12 +11441,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>70,64%</t>
+          <t>70,28%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>85,42%</t>
+          <t>84,76%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -11461,12 +11461,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>101858</t>
+          <t>101887</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>120948</t>
+          <t>120775</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -11476,12 +11476,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>66,38%</t>
+          <t>66,39%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>78,82%</t>
+          <t>78,7%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -11496,12 +11496,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>201988</t>
+          <t>201040</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>229652</t>
+          <t>229556</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -11511,12 +11511,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>70,39%</t>
+          <t>70,06%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>80,04%</t>
+          <t>80,0%</t>
         </is>
       </c>
     </row>
@@ -11656,97 +11656,97 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K22" s="2" t="inlineStr">
+        <is>
+          <t>1342</t>
+        </is>
+      </c>
+      <c r="L22" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>1728</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
+      <c r="M22" s="2" t="inlineStr">
+        <is>
+          <t>4862</t>
+        </is>
+      </c>
+      <c r="N22" s="2" t="inlineStr">
+        <is>
+          <t>0,15%</t>
+        </is>
+      </c>
+      <c r="O22" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H22" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I22" s="2" t="inlineStr">
-        <is>
-          <t>0,27%</t>
-        </is>
-      </c>
-      <c r="J22" s="2" t="inlineStr">
+      <c r="P22" s="2" t="inlineStr">
+        <is>
+          <t>0,54%</t>
+        </is>
+      </c>
+      <c r="Q22" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="K22" s="2" t="inlineStr">
+      <c r="R22" s="2" t="inlineStr">
         <is>
           <t>1342</t>
         </is>
       </c>
-      <c r="L22" s="2" t="inlineStr">
+      <c r="S22" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M22" s="2" t="inlineStr">
-        <is>
-          <t>4416</t>
-        </is>
-      </c>
-      <c r="N22" s="2" t="inlineStr">
-        <is>
-          <t>0,15%</t>
-        </is>
-      </c>
-      <c r="O22" s="2" t="inlineStr">
+      <c r="T22" s="2" t="inlineStr">
+        <is>
+          <t>4262</t>
+        </is>
+      </c>
+      <c r="U22" s="2" t="inlineStr">
+        <is>
+          <t>0,09%</t>
+        </is>
+      </c>
+      <c r="V22" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P22" s="2" t="inlineStr">
-        <is>
-          <t>0,49%</t>
-        </is>
-      </c>
-      <c r="Q22" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="R22" s="2" t="inlineStr">
-        <is>
-          <t>1342</t>
-        </is>
-      </c>
-      <c r="S22" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T22" s="2" t="inlineStr">
-        <is>
-          <t>4740</t>
-        </is>
-      </c>
-      <c r="U22" s="2" t="inlineStr">
-        <is>
-          <t>0,09%</t>
-        </is>
-      </c>
-      <c r="V22" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>0,31%</t>
+          <t>0,28%</t>
         </is>
       </c>
     </row>
@@ -11769,12 +11769,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>2924</t>
+          <t>2680</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>13403</t>
+          <t>13732</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -11784,12 +11784,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>0,46%</t>
+          <t>0,42%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>2,09%</t>
+          <t>2,14%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -11804,12 +11804,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>3461</t>
+          <t>3210</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>12359</t>
+          <t>11985</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -11819,12 +11819,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>0,39%</t>
+          <t>0,36%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>1,38%</t>
+          <t>1,34%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -11839,12 +11839,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>7920</t>
+          <t>8130</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>21633</t>
+          <t>20934</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -11854,12 +11854,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>0,52%</t>
+          <t>0,53%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>1,41%</t>
+          <t>1,36%</t>
         </is>
       </c>
     </row>
@@ -11882,12 +11882,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>21971</t>
+          <t>22204</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>47120</t>
+          <t>50119</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -11897,12 +11897,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>3,43%</t>
+          <t>3,47%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>7,35%</t>
+          <t>7,82%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -11917,12 +11917,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>33443</t>
+          <t>31840</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>59803</t>
+          <t>58159</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -11932,12 +11932,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>3,74%</t>
+          <t>3,56%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>6,69%</t>
+          <t>6,51%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -11952,12 +11952,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>58847</t>
+          <t>59181</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>97348</t>
+          <t>96198</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -11967,12 +11967,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>3,84%</t>
+          <t>3,86%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>6,35%</t>
+          <t>6,27%</t>
         </is>
       </c>
     </row>
@@ -11995,12 +11995,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>18314</t>
+          <t>18255</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>40460</t>
+          <t>37888</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -12010,12 +12010,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>2,86%</t>
+          <t>2,85%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>6,32%</t>
+          <t>5,91%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -12030,12 +12030,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>24689</t>
+          <t>24088</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>45020</t>
+          <t>45361</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -12045,12 +12045,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>2,76%</t>
+          <t>2,7%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>5,04%</t>
+          <t>5,08%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -12065,12 +12065,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>46688</t>
+          <t>45699</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>76447</t>
+          <t>76463</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -12080,7 +12080,7 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>3,04%</t>
+          <t>2,98%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
@@ -12108,12 +12108,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>556355</t>
+          <t>556762</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>589569</t>
+          <t>590180</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -12123,12 +12123,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>86,84%</t>
+          <t>86,91%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>92,03%</t>
+          <t>92,12%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -12143,12 +12143,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>787889</t>
+          <t>789926</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>826688</t>
+          <t>829885</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -12158,12 +12158,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>88,19%</t>
+          <t>88,42%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>92,53%</t>
+          <t>92,89%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -12178,12 +12178,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1356140</t>
+          <t>1356380</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1409275</t>
+          <t>1408990</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -12193,12 +12193,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>88,4%</t>
+          <t>88,42%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>91,87%</t>
+          <t>91,85%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P17G-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/P17G-Estudios-trans_orig.xlsx
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>2905</t>
+          <t>2899</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>13990</t>
+          <t>13205</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -866,7 +866,7 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>4,19%</t>
+          <t>3,95%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -886,7 +886,7 @@
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>6225</t>
+          <t>5267</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -901,7 +901,7 @@
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>1,18%</t>
+          <t>1,0%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>3602</t>
+          <t>3586</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>14831</t>
+          <t>14106</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -936,7 +936,7 @@
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>1,72%</t>
+          <t>1,64%</t>
         </is>
       </c>
     </row>
@@ -959,12 +959,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>1689</t>
+          <t>1772</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>10407</t>
+          <t>10059</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -974,12 +974,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>0,51%</t>
+          <t>0,53%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>3,11%</t>
+          <t>3,01%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -999,7 +999,7 @@
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>8101</t>
+          <t>7565</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1014,7 +1014,7 @@
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>1,53%</t>
+          <t>1,43%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1029,12 +1029,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>2900</t>
+          <t>2821</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>13992</t>
+          <t>14701</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1044,12 +1044,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>0,34%</t>
+          <t>0,33%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>1,62%</t>
+          <t>1,7%</t>
         </is>
       </c>
     </row>
@@ -1077,7 +1077,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>6743</t>
+          <t>6726</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1092,7 +1092,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>2,02%</t>
+          <t>2,01%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1107,12 +1107,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>2926</t>
+          <t>3341</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>14571</t>
+          <t>15176</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1122,12 +1122,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>0,55%</t>
+          <t>0,63%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>2,76%</t>
+          <t>2,87%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1142,12 +1142,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>4781</t>
+          <t>4130</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>17509</t>
+          <t>17056</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1157,12 +1157,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,55%</t>
+          <t>0,48%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>2,03%</t>
+          <t>1,98%</t>
         </is>
       </c>
     </row>
@@ -1185,12 +1185,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>311754</t>
+          <t>312883</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>326238</t>
+          <t>326125</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1200,12 +1200,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>93,29%</t>
+          <t>93,62%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>97,62%</t>
+          <t>97,59%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1220,12 +1220,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>508932</t>
+          <t>508843</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>523059</t>
+          <t>522474</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1235,12 +1235,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>96,38%</t>
+          <t>96,36%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>99,05%</t>
+          <t>98,94%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1255,12 +1255,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>826834</t>
+          <t>827918</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>846885</t>
+          <t>846883</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1270,7 +1270,7 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>95,89%</t>
+          <t>96,02%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -1528,12 +1528,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>2810</t>
+          <t>2797</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>13043</t>
+          <t>13190</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1548,7 +1548,7 @@
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>5,22%</t>
+          <t>5,28%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1563,12 +1563,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>3044</t>
+          <t>2992</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>15141</t>
+          <t>14088</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1578,12 +1578,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>0,75%</t>
+          <t>0,74%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>3,75%</t>
+          <t>3,49%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1598,12 +1598,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>7647</t>
+          <t>7773</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>23081</t>
+          <t>21843</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1613,12 +1613,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>1,17%</t>
+          <t>1,19%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>3,53%</t>
+          <t>3,34%</t>
         </is>
       </c>
     </row>
@@ -1641,12 +1641,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>5793</t>
+          <t>5740</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>20038</t>
+          <t>19558</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1656,12 +1656,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>2,32%</t>
+          <t>2,3%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>8,02%</t>
+          <t>7,83%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1676,12 +1676,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>11260</t>
+          <t>10868</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>28002</t>
+          <t>28937</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1691,12 +1691,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>2,79%</t>
+          <t>2,69%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>6,93%</t>
+          <t>7,16%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1711,12 +1711,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>20765</t>
+          <t>19672</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>42876</t>
+          <t>41364</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1726,12 +1726,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>3,18%</t>
+          <t>3,01%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>6,56%</t>
+          <t>6,32%</t>
         </is>
       </c>
     </row>
@@ -1754,12 +1754,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>4357</t>
+          <t>4736</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>17090</t>
+          <t>16785</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1769,12 +1769,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,74%</t>
+          <t>1,9%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>6,84%</t>
+          <t>6,72%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1789,12 +1789,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>3747</t>
+          <t>3007</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>15559</t>
+          <t>15188</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1804,12 +1804,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>0,93%</t>
+          <t>0,74%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>3,85%</t>
+          <t>3,76%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1824,12 +1824,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>10805</t>
+          <t>10372</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>26944</t>
+          <t>26818</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1839,12 +1839,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>1,65%</t>
+          <t>1,59%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>4,12%</t>
+          <t>4,1%</t>
         </is>
       </c>
     </row>
@@ -1867,12 +1867,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>210516</t>
+          <t>211077</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>231164</t>
+          <t>231372</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1882,12 +1882,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>84,26%</t>
+          <t>84,48%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>92,52%</t>
+          <t>92,6%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1902,12 +1902,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>358781</t>
+          <t>359638</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>380752</t>
+          <t>382463</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1917,12 +1917,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>88,77%</t>
+          <t>88,99%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>94,21%</t>
+          <t>94,63%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1937,12 +1937,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>575832</t>
+          <t>578368</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>606466</t>
+          <t>608139</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1952,12 +1952,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>88,05%</t>
+          <t>88,44%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>92,73%</t>
+          <t>92,99%</t>
         </is>
       </c>
     </row>
@@ -2215,7 +2215,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>7423</t>
+          <t>6761</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2230,7 +2230,7 @@
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>10,34%</t>
+          <t>9,42%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2250,7 +2250,7 @@
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>6735</t>
+          <t>6810</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2265,7 +2265,7 @@
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>5,8%</t>
+          <t>5,86%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2280,12 +2280,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1003</t>
+          <t>1020</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>10548</t>
+          <t>10040</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2295,12 +2295,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>0,53%</t>
+          <t>0,54%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>5,61%</t>
+          <t>5,34%</t>
         </is>
       </c>
     </row>
@@ -2323,12 +2323,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>7075</t>
+          <t>7303</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>22159</t>
+          <t>21765</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2338,12 +2338,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>9,86%</t>
+          <t>10,18%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>30,88%</t>
+          <t>30,33%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2358,12 +2358,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>4161</t>
+          <t>4406</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>17389</t>
+          <t>17230</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2373,12 +2373,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>3,58%</t>
+          <t>3,79%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>14,97%</t>
+          <t>14,83%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2393,12 +2393,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>14032</t>
+          <t>13932</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>34224</t>
+          <t>34999</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2408,12 +2408,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>7,47%</t>
+          <t>7,41%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>18,21%</t>
+          <t>18,62%</t>
         </is>
       </c>
     </row>
@@ -2436,12 +2436,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>1927</t>
+          <t>1809</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>10842</t>
+          <t>11355</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2451,12 +2451,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>2,68%</t>
+          <t>2,52%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>15,11%</t>
+          <t>15,82%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2471,12 +2471,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>5367</t>
+          <t>5711</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>18662</t>
+          <t>19275</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2486,12 +2486,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>4,62%</t>
+          <t>4,92%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>16,07%</t>
+          <t>16,59%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2506,12 +2506,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>9393</t>
+          <t>9210</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>25312</t>
+          <t>24696</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2521,12 +2521,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>5,0%</t>
+          <t>4,9%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>13,47%</t>
+          <t>13,14%</t>
         </is>
       </c>
     </row>
@@ -2549,12 +2549,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>40861</t>
+          <t>41242</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>58100</t>
+          <t>58205</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2564,12 +2564,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>56,93%</t>
+          <t>57,46%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>80,95%</t>
+          <t>81,1%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2584,12 +2584,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>84060</t>
+          <t>83729</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>102740</t>
+          <t>101624</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2599,12 +2599,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>72,37%</t>
+          <t>72,09%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>88,46%</t>
+          <t>87,49%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2619,12 +2619,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>132664</t>
+          <t>132723</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>156188</t>
+          <t>156840</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2634,12 +2634,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>70,6%</t>
+          <t>70,63%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>83,12%</t>
+          <t>83,46%</t>
         </is>
       </c>
     </row>
@@ -2892,12 +2892,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>8798</t>
+          <t>9397</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>23854</t>
+          <t>24143</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2907,12 +2907,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>1,34%</t>
+          <t>1,43%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>3,64%</t>
+          <t>3,68%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2927,12 +2927,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>4941</t>
+          <t>4960</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>17098</t>
+          <t>17518</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2947,7 +2947,7 @@
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>1,63%</t>
+          <t>1,67%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2962,12 +2962,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>17145</t>
+          <t>16400</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>36974</t>
+          <t>35903</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2977,12 +2977,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>1,01%</t>
+          <t>0,96%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>2,17%</t>
+          <t>2,11%</t>
         </is>
       </c>
     </row>
@@ -3005,12 +3005,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>20450</t>
+          <t>19455</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>42519</t>
+          <t>42523</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3020,7 +3020,7 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>3,12%</t>
+          <t>2,97%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
@@ -3040,12 +3040,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>19124</t>
+          <t>19787</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>41817</t>
+          <t>42258</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3055,12 +3055,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>1,82%</t>
+          <t>1,89%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>3,99%</t>
+          <t>4,03%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3075,12 +3075,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>44864</t>
+          <t>43879</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>75896</t>
+          <t>75188</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3090,12 +3090,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>2,63%</t>
+          <t>2,57%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>4,45%</t>
+          <t>4,41%</t>
         </is>
       </c>
     </row>
@@ -3118,12 +3118,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>10375</t>
+          <t>9885</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>27078</t>
+          <t>26428</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3133,12 +3133,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>1,58%</t>
+          <t>1,51%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>4,13%</t>
+          <t>4,03%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3153,12 +3153,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>16555</t>
+          <t>16984</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>37560</t>
+          <t>37494</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3168,7 +3168,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>1,58%</t>
+          <t>1,62%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3188,12 +3188,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>32233</t>
+          <t>30330</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>58534</t>
+          <t>55829</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3203,12 +3203,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>1,89%</t>
+          <t>1,78%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>3,43%</t>
+          <t>3,28%</t>
         </is>
       </c>
     </row>
@@ -3231,12 +3231,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>576484</t>
+          <t>576662</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>607664</t>
+          <t>607753</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3246,12 +3246,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>87,9%</t>
+          <t>87,93%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>92,66%</t>
+          <t>92,67%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3266,12 +3266,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>964140</t>
+          <t>965119</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>997163</t>
+          <t>997968</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3281,12 +3281,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>91,97%</t>
+          <t>92,06%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>95,12%</t>
+          <t>95,19%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3301,12 +3301,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1552659</t>
+          <t>1556823</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1598206</t>
+          <t>1599828</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3316,12 +3316,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>91,11%</t>
+          <t>91,35%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>93,78%</t>
+          <t>93,88%</t>
         </is>
       </c>
     </row>
@@ -3697,7 +3697,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>4593</t>
+          <t>6226</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3712,7 +3712,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>1,36%</t>
+          <t>1,84%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3767,7 +3767,7 @@
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>5327</t>
+          <t>4109</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3782,7 +3782,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>0,61%</t>
+          <t>0,47%</t>
         </is>
       </c>
     </row>
@@ -3805,12 +3805,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>937</t>
+          <t>958</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>9659</t>
+          <t>10133</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3825,7 +3825,7 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>2,86%</t>
+          <t>3,0%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -3845,7 +3845,7 @@
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>4763</t>
+          <t>5166</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -3860,7 +3860,7 @@
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>0,88%</t>
+          <t>0,95%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3875,12 +3875,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>962</t>
+          <t>986</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>10410</t>
+          <t>10898</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3895,7 +3895,7 @@
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>1,18%</t>
+          <t>1,24%</t>
         </is>
       </c>
     </row>
@@ -3918,12 +3918,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>1097</t>
+          <t>1028</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>10638</t>
+          <t>9615</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -3933,12 +3933,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>0,32%</t>
+          <t>0,3%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>3,15%</t>
+          <t>2,85%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -3953,12 +3953,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>3162</t>
+          <t>2981</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>14950</t>
+          <t>13773</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -3968,12 +3968,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>0,58%</t>
+          <t>0,55%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>2,76%</t>
+          <t>2,54%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -3988,12 +3988,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>5996</t>
+          <t>6214</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>19770</t>
+          <t>20097</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -4003,12 +4003,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>0,68%</t>
+          <t>0,71%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>2,25%</t>
+          <t>2,29%</t>
         </is>
       </c>
     </row>
@@ -4031,12 +4031,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>940</t>
+          <t>946</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>7940</t>
+          <t>8028</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4051,7 +4051,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>2,35%</t>
+          <t>2,38%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4066,12 +4066,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>888</t>
+          <t>890</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>8071</t>
+          <t>8110</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4086,7 +4086,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>1,49%</t>
+          <t>1,5%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4101,12 +4101,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>1990</t>
+          <t>2089</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>11952</t>
+          <t>12841</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4116,12 +4116,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,23%</t>
+          <t>0,24%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>1,36%</t>
+          <t>1,46%</t>
         </is>
       </c>
     </row>
@@ -4144,12 +4144,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>316881</t>
+          <t>317466</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>330932</t>
+          <t>331380</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4159,12 +4159,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>93,9%</t>
+          <t>94,07%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>98,06%</t>
+          <t>98,19%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4179,12 +4179,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>521620</t>
+          <t>522034</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>535222</t>
+          <t>535291</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4194,12 +4194,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>96,39%</t>
+          <t>96,46%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>98,9%</t>
+          <t>98,91%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4214,12 +4214,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>844723</t>
+          <t>845368</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>864161</t>
+          <t>863940</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4229,12 +4229,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>96,14%</t>
+          <t>96,21%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>98,35%</t>
+          <t>98,32%</t>
         </is>
       </c>
     </row>
@@ -4487,12 +4487,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>785</t>
+          <t>800</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>7410</t>
+          <t>8075</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4502,12 +4502,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>0,22%</t>
+          <t>0,23%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>2,08%</t>
+          <t>2,27%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4557,12 +4557,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>804</t>
+          <t>799</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>7144</t>
+          <t>7429</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4572,12 +4572,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>0,1%</t>
+          <t>0,09%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>0,85%</t>
+          <t>0,88%</t>
         </is>
       </c>
     </row>
@@ -4600,12 +4600,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>3807</t>
+          <t>3887</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>14542</t>
+          <t>14546</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -4615,7 +4615,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>1,07%</t>
+          <t>1,09%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -4635,12 +4635,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>4846</t>
+          <t>3987</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>17053</t>
+          <t>15941</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -4650,12 +4650,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>1,0%</t>
+          <t>0,82%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>3,5%</t>
+          <t>3,28%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -4670,12 +4670,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>9871</t>
+          <t>10005</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>25963</t>
+          <t>26837</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -4685,12 +4685,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>1,17%</t>
+          <t>1,19%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>3,08%</t>
+          <t>3,19%</t>
         </is>
       </c>
     </row>
@@ -4713,12 +4713,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>8750</t>
+          <t>8883</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>28686</t>
+          <t>27371</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4728,12 +4728,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>2,46%</t>
+          <t>2,5%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>8,07%</t>
+          <t>7,7%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -4748,12 +4748,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>1115</t>
+          <t>1801</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>12326</t>
+          <t>12445</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -4763,12 +4763,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>0,23%</t>
+          <t>0,37%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>2,53%</t>
+          <t>2,56%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4783,12 +4783,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>12604</t>
+          <t>12597</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>34012</t>
+          <t>34453</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4803,7 +4803,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>4,04%</t>
+          <t>4,09%</t>
         </is>
       </c>
     </row>
@@ -4826,12 +4826,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>316121</t>
+          <t>315927</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>338139</t>
+          <t>337960</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4841,12 +4841,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>88,92%</t>
+          <t>88,86%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>95,11%</t>
+          <t>95,06%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4861,12 +4861,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>463256</t>
+          <t>464785</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>478594</t>
+          <t>479492</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4876,12 +4876,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>95,21%</t>
+          <t>95,53%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>98,36%</t>
+          <t>98,55%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -4896,12 +4896,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>785971</t>
+          <t>786209</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>813242</t>
+          <t>813220</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4911,12 +4911,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>93,34%</t>
+          <t>93,37%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>96,58%</t>
+          <t>96,57%</t>
         </is>
       </c>
     </row>
@@ -5174,7 +5174,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>4585</t>
+          <t>5583</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5189,7 +5189,7 @@
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>6,13%</t>
+          <t>7,46%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5209,7 +5209,7 @@
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>8892</t>
+          <t>10143</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5224,7 +5224,7 @@
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>8,25%</t>
+          <t>9,41%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5244,7 +5244,7 @@
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>9595</t>
+          <t>9902</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5259,7 +5259,7 @@
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>5,26%</t>
+          <t>5,42%</t>
         </is>
       </c>
     </row>
@@ -5282,12 +5282,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>2988</t>
+          <t>2228</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>15613</t>
+          <t>15047</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -5297,12 +5297,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>3,99%</t>
+          <t>2,98%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>20,87%</t>
+          <t>20,11%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -5317,12 +5317,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>880</t>
+          <t>879</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>7693</t>
+          <t>7499</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -5337,7 +5337,7 @@
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>7,14%</t>
+          <t>6,96%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -5352,12 +5352,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>4883</t>
+          <t>4733</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>20418</t>
+          <t>18297</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -5367,12 +5367,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>2,67%</t>
+          <t>2,59%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>11,18%</t>
+          <t>10,02%</t>
         </is>
       </c>
     </row>
@@ -5395,12 +5395,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>2009</t>
+          <t>2051</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>10935</t>
+          <t>12097</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5410,12 +5410,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>2,68%</t>
+          <t>2,74%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>14,62%</t>
+          <t>16,17%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5430,12 +5430,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>9249</t>
+          <t>9734</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>27019</t>
+          <t>26575</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5445,12 +5445,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>8,59%</t>
+          <t>9,04%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>25,08%</t>
+          <t>24,67%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5465,12 +5465,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>13667</t>
+          <t>13927</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>32919</t>
+          <t>32853</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5480,12 +5480,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>7,49%</t>
+          <t>7,63%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>18,03%</t>
+          <t>18,0%</t>
         </is>
       </c>
     </row>
@@ -5508,12 +5508,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>52814</t>
+          <t>54076</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>67515</t>
+          <t>67665</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5523,12 +5523,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>70,59%</t>
+          <t>72,27%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>90,24%</t>
+          <t>90,44%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5543,12 +5543,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>76347</t>
+          <t>76112</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>94203</t>
+          <t>94719</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5558,12 +5558,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>70,87%</t>
+          <t>70,65%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>87,44%</t>
+          <t>87,92%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5578,12 +5578,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>134153</t>
+          <t>135180</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>157551</t>
+          <t>158077</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5593,12 +5593,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>73,49%</t>
+          <t>74,05%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>86,31%</t>
+          <t>86,59%</t>
         </is>
       </c>
     </row>
@@ -5743,7 +5743,7 @@
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>5154</t>
+          <t>4601</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5758,7 +5758,7 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>0,67%</t>
+          <t>0,6%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5813,7 +5813,7 @@
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>4601</t>
+          <t>5152</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5828,7 +5828,7 @@
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>0,24%</t>
+          <t>0,27%</t>
         </is>
       </c>
     </row>
@@ -5851,12 +5851,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>2919</t>
+          <t>3314</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>14723</t>
+          <t>14630</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -5866,12 +5866,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>0,38%</t>
+          <t>0,43%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>1,92%</t>
+          <t>1,91%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -5891,7 +5891,7 @@
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>9882</t>
+          <t>10570</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -5906,7 +5906,7 @@
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>0,87%</t>
+          <t>0,93%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -5921,12 +5921,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>4760</t>
+          <t>4794</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>18865</t>
+          <t>19063</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -5941,7 +5941,7 @@
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>0,99%</t>
+          <t>1,0%</t>
         </is>
       </c>
     </row>
@@ -5964,12 +5964,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>11233</t>
+          <t>11501</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>30481</t>
+          <t>30091</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -5979,12 +5979,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>1,46%</t>
+          <t>1,5%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>3,97%</t>
+          <t>3,92%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -5999,12 +5999,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>11936</t>
+          <t>11317</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>30354</t>
+          <t>28234</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -6014,12 +6014,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>1,05%</t>
+          <t>1,0%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>2,67%</t>
+          <t>2,49%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -6034,12 +6034,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>27673</t>
+          <t>28004</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>52400</t>
+          <t>52297</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -6049,7 +6049,7 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>1,45%</t>
+          <t>1,47%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
@@ -6077,12 +6077,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>15205</t>
+          <t>15249</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>38537</t>
+          <t>38843</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6092,12 +6092,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>1,98%</t>
+          <t>1,99%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>5,02%</t>
+          <t>5,06%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6112,12 +6112,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>14718</t>
+          <t>15152</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>37116</t>
+          <t>35644</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6127,12 +6127,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>1,3%</t>
+          <t>1,33%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>3,27%</t>
+          <t>3,14%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6147,12 +6147,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>35345</t>
+          <t>35167</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>67153</t>
+          <t>66425</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6162,12 +6162,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>1,86%</t>
+          <t>1,85%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>3,53%</t>
+          <t>3,49%</t>
         </is>
       </c>
     </row>
@@ -6190,12 +6190,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>699275</t>
+          <t>698715</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>729420</t>
+          <t>729753</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6205,12 +6205,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>91,07%</t>
+          <t>91,0%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>95,0%</t>
+          <t>95,04%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6225,12 +6225,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>1073072</t>
+          <t>1073713</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>1101984</t>
+          <t>1102090</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6240,12 +6240,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>94,5%</t>
+          <t>94,56%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>97,05%</t>
+          <t>97,06%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6260,12 +6260,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1782153</t>
+          <t>1781570</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1825030</t>
+          <t>1823694</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6275,12 +6275,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>93,64%</t>
+          <t>93,6%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>95,89%</t>
+          <t>95,82%</t>
         </is>
       </c>
     </row>
@@ -6804,7 +6804,7 @@
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>6614</t>
+          <t>6966</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -6819,7 +6819,7 @@
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>1,61%</t>
+          <t>1,69%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6839,7 +6839,7 @@
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>7045</t>
+          <t>6865</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -6854,7 +6854,7 @@
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>1,05%</t>
+          <t>1,03%</t>
         </is>
       </c>
     </row>
@@ -6912,12 +6912,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>1135</t>
+          <t>1150</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>12247</t>
+          <t>11580</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -6932,7 +6932,7 @@
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>2,98%</t>
+          <t>2,82%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -6947,12 +6947,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>1132</t>
+          <t>1133</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>12440</t>
+          <t>11666</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -6967,7 +6967,7 @@
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>1,86%</t>
+          <t>1,74%</t>
         </is>
       </c>
     </row>
@@ -6990,12 +6990,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>2051</t>
+          <t>2045</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>11678</t>
+          <t>12476</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -7010,7 +7010,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>4,52%</t>
+          <t>4,83%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -7025,12 +7025,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>3339</t>
+          <t>3332</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>14987</t>
+          <t>16806</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -7045,7 +7045,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>3,64%</t>
+          <t>4,09%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -7060,12 +7060,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>7147</t>
+          <t>7309</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>22354</t>
+          <t>22382</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7075,7 +7075,7 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>1,07%</t>
+          <t>1,09%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
@@ -7103,12 +7103,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>246586</t>
+          <t>245788</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>256213</t>
+          <t>256219</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -7118,7 +7118,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>95,48%</t>
+          <t>95,17%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -7138,12 +7138,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>387863</t>
+          <t>386688</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>404269</t>
+          <t>403689</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -7153,12 +7153,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>94,31%</t>
+          <t>94,02%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>98,3%</t>
+          <t>98,15%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7173,12 +7173,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>640013</t>
+          <t>639759</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>657805</t>
+          <t>657811</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -7188,7 +7188,7 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>95,59%</t>
+          <t>95,55%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -7338,7 +7338,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>5728</t>
+          <t>5445</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -7353,7 +7353,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>1,24%</t>
+          <t>1,18%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -7408,7 +7408,7 @@
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>4950</t>
+          <t>4934</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -7446,12 +7446,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>3838</t>
+          <t>3789</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>14859</t>
+          <t>15289</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -7461,12 +7461,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>0,83%</t>
+          <t>0,82%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>3,23%</t>
+          <t>3,32%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -7486,7 +7486,7 @@
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>7143</t>
+          <t>6966</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -7501,7 +7501,7 @@
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>1,22%</t>
+          <t>1,19%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -7516,12 +7516,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>4849</t>
+          <t>4834</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>17552</t>
+          <t>17405</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -7536,7 +7536,7 @@
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>1,68%</t>
+          <t>1,67%</t>
         </is>
       </c>
     </row>
@@ -7559,12 +7559,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>4323</t>
+          <t>4304</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>18346</t>
+          <t>18755</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -7574,12 +7574,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>0,94%</t>
+          <t>0,93%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>3,98%</t>
+          <t>4,07%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -7594,12 +7594,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>5420</t>
+          <t>5701</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>20581</t>
+          <t>20195</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -7609,12 +7609,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>0,93%</t>
+          <t>0,98%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>3,52%</t>
+          <t>3,46%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -7629,12 +7629,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>12335</t>
+          <t>13269</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>30844</t>
+          <t>33813</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -7644,12 +7644,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>1,18%</t>
+          <t>1,27%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>2,95%</t>
+          <t>3,24%</t>
         </is>
       </c>
     </row>
@@ -7672,12 +7672,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>14875</t>
+          <t>15525</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>35656</t>
+          <t>36080</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -7687,12 +7687,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>3,23%</t>
+          <t>3,37%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>7,74%</t>
+          <t>7,83%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7707,12 +7707,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>11665</t>
+          <t>11468</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>29513</t>
+          <t>29750</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -7722,12 +7722,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>2,0%</t>
+          <t>1,96%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>5,05%</t>
+          <t>5,09%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7742,12 +7742,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>31396</t>
+          <t>32064</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>59220</t>
+          <t>60376</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -7757,12 +7757,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>3,0%</t>
+          <t>3,07%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>5,67%</t>
+          <t>5,78%</t>
         </is>
       </c>
     </row>
@@ -7785,12 +7785,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>402754</t>
+          <t>402885</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>429659</t>
+          <t>429406</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -7800,12 +7800,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>87,43%</t>
+          <t>87,45%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>93,27%</t>
+          <t>93,21%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7820,12 +7820,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>538828</t>
+          <t>539381</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>561594</t>
+          <t>562302</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -7835,12 +7835,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>92,22%</t>
+          <t>92,32%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>96,12%</t>
+          <t>96,24%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7855,12 +7855,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>951969</t>
+          <t>951209</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>987510</t>
+          <t>986068</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -7870,12 +7870,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>91,1%</t>
+          <t>91,03%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>94,5%</t>
+          <t>94,36%</t>
         </is>
       </c>
     </row>
@@ -8128,12 +8128,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>966</t>
+          <t>968</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>8450</t>
+          <t>7869</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -8148,7 +8148,7 @@
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>7,0%</t>
+          <t>6,52%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8168,7 +8168,7 @@
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>3621</t>
+          <t>4467</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -8183,7 +8183,7 @@
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>2,61%</t>
+          <t>3,22%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8198,12 +8198,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1132</t>
+          <t>997</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>10166</t>
+          <t>9638</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8213,12 +8213,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>0,44%</t>
+          <t>0,38%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>3,92%</t>
+          <t>3,72%</t>
         </is>
       </c>
     </row>
@@ -8241,12 +8241,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>2709</t>
+          <t>2892</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>13518</t>
+          <t>13721</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -8256,12 +8256,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>2,24%</t>
+          <t>2,4%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>11,2%</t>
+          <t>11,37%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -8276,12 +8276,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>1064</t>
+          <t>1074</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>9375</t>
+          <t>9721</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -8296,7 +8296,7 @@
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>6,76%</t>
+          <t>7,01%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -8311,12 +8311,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>5784</t>
+          <t>5166</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>20865</t>
+          <t>18510</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -8326,12 +8326,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>2,23%</t>
+          <t>1,99%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>8,05%</t>
+          <t>7,14%</t>
         </is>
       </c>
     </row>
@@ -8354,12 +8354,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>8974</t>
+          <t>9412</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>24918</t>
+          <t>25733</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -8369,12 +8369,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>7,43%</t>
+          <t>7,8%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>20,64%</t>
+          <t>21,32%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -8389,12 +8389,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>11563</t>
+          <t>11735</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>28815</t>
+          <t>29480</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -8404,12 +8404,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>8,34%</t>
+          <t>8,47%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>20,79%</t>
+          <t>21,27%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -8424,12 +8424,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>25240</t>
+          <t>23806</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>48514</t>
+          <t>46763</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -8439,12 +8439,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>9,73%</t>
+          <t>9,18%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>18,71%</t>
+          <t>18,03%</t>
         </is>
       </c>
     </row>
@@ -8467,12 +8467,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>85274</t>
+          <t>84276</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>104665</t>
+          <t>103385</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -8482,12 +8482,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>70,65%</t>
+          <t>69,82%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>86,71%</t>
+          <t>85,65%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -8502,12 +8502,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>103646</t>
+          <t>103077</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>122820</t>
+          <t>122815</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -8517,7 +8517,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>74,77%</t>
+          <t>74,36%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -8537,12 +8537,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>194047</t>
+          <t>195922</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>221226</t>
+          <t>223444</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -8552,12 +8552,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>74,83%</t>
+          <t>75,55%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>85,31%</t>
+          <t>86,16%</t>
         </is>
       </c>
     </row>
@@ -8702,7 +8702,7 @@
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>6438</t>
+          <t>6504</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -8772,7 +8772,7 @@
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>5665</t>
+          <t>4915</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -8787,7 +8787,7 @@
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>0,29%</t>
+          <t>0,25%</t>
         </is>
       </c>
     </row>
@@ -8810,12 +8810,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>5898</t>
+          <t>5784</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>18867</t>
+          <t>19256</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -8825,12 +8825,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>0,69%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>2,25%</t>
+          <t>2,29%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -8845,12 +8845,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>1763</t>
+          <t>1811</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>10630</t>
+          <t>11882</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -8865,7 +8865,7 @@
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>0,94%</t>
+          <t>1,05%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -8880,12 +8880,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>9748</t>
+          <t>9311</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>24831</t>
+          <t>25529</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -8895,12 +8895,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>0,49%</t>
+          <t>0,47%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>1,26%</t>
+          <t>1,29%</t>
         </is>
       </c>
     </row>
@@ -8923,12 +8923,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>8771</t>
+          <t>9320</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>26341</t>
+          <t>26591</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -8938,12 +8938,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>1,04%</t>
+          <t>1,11%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>3,14%</t>
+          <t>3,17%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -8958,12 +8958,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>11609</t>
+          <t>10994</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>30120</t>
+          <t>29662</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -8973,12 +8973,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>1,02%</t>
+          <t>0,97%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>2,66%</t>
+          <t>2,62%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -8993,12 +8993,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>24582</t>
+          <t>24116</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>50426</t>
+          <t>49885</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -9008,12 +9008,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>1,25%</t>
+          <t>1,22%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>2,55%</t>
+          <t>2,53%</t>
         </is>
       </c>
     </row>
@@ -9036,12 +9036,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>32695</t>
+          <t>33308</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>60268</t>
+          <t>61309</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -9051,12 +9051,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>3,89%</t>
+          <t>3,97%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>7,18%</t>
+          <t>7,3%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -9071,12 +9071,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>33405</t>
+          <t>33899</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>61928</t>
+          <t>61468</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -9086,12 +9086,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>2,95%</t>
+          <t>2,99%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>5,46%</t>
+          <t>5,42%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -9106,12 +9106,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>72926</t>
+          <t>73430</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>112922</t>
+          <t>113776</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -9121,12 +9121,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>3,69%</t>
+          <t>3,72%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>5,72%</t>
+          <t>5,76%</t>
         </is>
       </c>
     </row>
@@ -9149,12 +9149,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>748469</t>
+          <t>747805</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>782572</t>
+          <t>781025</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -9164,12 +9164,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>89,14%</t>
+          <t>89,06%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>93,2%</t>
+          <t>93,02%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -9184,12 +9184,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>1045157</t>
+          <t>1046724</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>1078616</t>
+          <t>1080629</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -9199,12 +9199,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>92,15%</t>
+          <t>92,29%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>95,1%</t>
+          <t>95,28%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -9219,12 +9219,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1802101</t>
+          <t>1804681</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1851859</t>
+          <t>1852713</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -9234,12 +9234,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>91,3%</t>
+          <t>91,43%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>93,82%</t>
+          <t>93,86%</t>
         </is>
       </c>
     </row>
@@ -9831,7 +9831,7 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>452</t>
+          <t>454</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
@@ -9841,12 +9841,12 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>2216</t>
+          <t>2625</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>0,33%</t>
+          <t>0,31%</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
@@ -9856,7 +9856,7 @@
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>1,61%</t>
+          <t>1,78%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -9866,32 +9866,32 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>2880</t>
+          <t>3019</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>1017</t>
+          <t>1211</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>6096</t>
+          <t>6806</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>1,21%</t>
+          <t>1,17%</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>0,43%</t>
+          <t>0,47%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>2,57%</t>
+          <t>2,64%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -9901,32 +9901,32 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>3332</t>
+          <t>3472</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>1430</t>
+          <t>1444</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>6916</t>
+          <t>7370</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
         <is>
-          <t>0,89%</t>
+          <t>0,86%</t>
         </is>
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>0,38%</t>
+          <t>0,36%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>1,84%</t>
+          <t>1,82%</t>
         </is>
       </c>
     </row>
@@ -9944,7 +9944,7 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>1477</t>
+          <t>1620</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
@@ -9954,12 +9954,12 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>5231</t>
+          <t>4993</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>1,07%</t>
+          <t>1,1%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
@@ -9969,7 +9969,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>3,8%</t>
+          <t>3,39%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -9979,32 +9979,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>2518</t>
+          <t>2779</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>552</t>
+          <t>625</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>6424</t>
+          <t>7561</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>1,06%</t>
+          <t>1,08%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>0,23%</t>
+          <t>0,24%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>2,7%</t>
+          <t>2,94%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -10014,32 +10014,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>3995</t>
+          <t>4400</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>1570</t>
+          <t>1583</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>8731</t>
+          <t>9626</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>1,06%</t>
+          <t>1,09%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,42%</t>
+          <t>0,39%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>2,33%</t>
+          <t>2,38%</t>
         </is>
       </c>
     </row>
@@ -10057,32 +10057,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>135582</t>
+          <t>145066</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>132311</t>
+          <t>141297</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>137057</t>
+          <t>146677</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>98,6%</t>
+          <t>98,59%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>96,22%</t>
+          <t>96,03%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>99,67%</t>
+          <t>99,69%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -10092,32 +10092,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>232204</t>
+          <t>251517</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>227733</t>
+          <t>246334</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>234790</t>
+          <t>254606</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>97,73%</t>
+          <t>97,75%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>95,85%</t>
+          <t>95,73%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>98,82%</t>
+          <t>98,95%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -10127,17 +10127,17 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>367787</t>
+          <t>396583</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>362201</t>
+          <t>390767</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>371072</t>
+          <t>400386</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -10147,12 +10147,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>96,56%</t>
+          <t>96,62%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>98,92%</t>
+          <t>98,99%</t>
         </is>
       </c>
     </row>
@@ -10170,17 +10170,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>137511</t>
+          <t>147140</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>137511</t>
+          <t>147140</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>137511</t>
+          <t>147140</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -10205,17 +10205,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>237602</t>
+          <t>257315</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>237602</t>
+          <t>257315</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>237602</t>
+          <t>257315</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -10240,17 +10240,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>375114</t>
+          <t>404455</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>375114</t>
+          <t>404455</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>375114</t>
+          <t>404455</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -10322,7 +10322,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>1342</t>
+          <t>1378</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
@@ -10332,12 +10332,12 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>4792</t>
+          <t>4878</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>0,27%</t>
+          <t>0,28%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
@@ -10347,7 +10347,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>0,95%</t>
+          <t>1,0%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -10357,7 +10357,7 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>1342</t>
+          <t>1378</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
@@ -10367,12 +10367,12 @@
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>4434</t>
+          <t>4867</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>0,15%</t>
+          <t>0,16%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
@@ -10382,7 +10382,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>0,51%</t>
+          <t>0,55%</t>
         </is>
       </c>
     </row>
@@ -10400,102 +10400,102 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>4573</t>
+          <t>6189</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>1244</t>
+          <t>2309</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>10240</t>
+          <t>13993</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
+          <t>1,56%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>0,58%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>3,53%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>4768</t>
+        </is>
+      </c>
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>2044</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>9852</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
+        <is>
+          <t>0,97%</t>
+        </is>
+      </c>
+      <c r="O11" s="2" t="inlineStr">
+        <is>
+          <t>0,42%</t>
+        </is>
+      </c>
+      <c r="P11" s="2" t="inlineStr">
+        <is>
+          <t>2,01%</t>
+        </is>
+      </c>
+      <c r="Q11" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="R11" s="2" t="inlineStr">
+        <is>
+          <t>10957</t>
+        </is>
+      </c>
+      <c r="S11" s="2" t="inlineStr">
+        <is>
+          <t>5239</t>
+        </is>
+      </c>
+      <c r="T11" s="2" t="inlineStr">
+        <is>
+          <t>19769</t>
+        </is>
+      </c>
+      <c r="U11" s="2" t="inlineStr">
+        <is>
           <t>1,24%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>0,34%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>2,77%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>4429</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>1717</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>9672</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>0,88%</t>
-        </is>
-      </c>
-      <c r="O11" s="2" t="inlineStr">
-        <is>
-          <t>0,34%</t>
-        </is>
-      </c>
-      <c r="P11" s="2" t="inlineStr">
-        <is>
-          <t>1,93%</t>
-        </is>
-      </c>
-      <c r="Q11" s="2" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="R11" s="2" t="inlineStr">
-        <is>
-          <t>9002</t>
-        </is>
-      </c>
-      <c r="S11" s="2" t="inlineStr">
-        <is>
-          <t>4555</t>
-        </is>
-      </c>
-      <c r="T11" s="2" t="inlineStr">
-        <is>
-          <t>16898</t>
-        </is>
-      </c>
-      <c r="U11" s="2" t="inlineStr">
-        <is>
-          <t>1,03%</t>
-        </is>
-      </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>0,52%</t>
+          <t>0,59%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>1,94%</t>
+          <t>2,23%</t>
         </is>
       </c>
     </row>
@@ -10513,32 +10513,32 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>16960</t>
+          <t>17319</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>8865</t>
+          <t>8745</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>31600</t>
+          <t>29489</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>4,59%</t>
+          <t>4,37%</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>2,4%</t>
+          <t>2,21%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>8,55%</t>
+          <t>7,44%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -10548,32 +10548,32 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>18779</t>
+          <t>21776</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>10321</t>
+          <t>14476</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>28257</t>
+          <t>32211</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>3,74%</t>
+          <t>4,45%</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>2,05%</t>
+          <t>2,96%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>5,63%</t>
+          <t>6,58%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -10583,32 +10583,32 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>35739</t>
+          <t>39095</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>23618</t>
+          <t>27652</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>51502</t>
+          <t>54932</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
         <is>
-          <t>4,1%</t>
+          <t>4,41%</t>
         </is>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>2,71%</t>
+          <t>3,12%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>5,91%</t>
+          <t>6,2%</t>
         </is>
       </c>
     </row>
@@ -10626,32 +10626,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>14056</t>
+          <t>15539</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>8265</t>
+          <t>9157</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>23711</t>
+          <t>25951</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>3,8%</t>
+          <t>3,92%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>2,24%</t>
+          <t>2,31%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>6,41%</t>
+          <t>6,55%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -10661,32 +10661,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>15259</t>
+          <t>15946</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>8625</t>
+          <t>10390</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>23728</t>
+          <t>23560</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>3,04%</t>
+          <t>3,26%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>1,72%</t>
+          <t>2,12%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>4,72%</t>
+          <t>4,81%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -10696,32 +10696,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>29314</t>
+          <t>31485</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>19893</t>
+          <t>23233</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>40986</t>
+          <t>44946</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>3,36%</t>
+          <t>3,55%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>2,28%</t>
+          <t>2,62%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>4,7%</t>
+          <t>5,07%</t>
         </is>
       </c>
     </row>
@@ -10739,32 +10739,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>334069</t>
+          <t>357184</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>319036</t>
+          <t>341940</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>345029</t>
+          <t>368676</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>90,37%</t>
+          <t>90,15%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>86,31%</t>
+          <t>86,3%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>93,34%</t>
+          <t>93,05%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -10774,32 +10774,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>462531</t>
+          <t>445659</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>449076</t>
+          <t>433297</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>479076</t>
+          <t>455623</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>92,08%</t>
+          <t>91,04%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>89,4%</t>
+          <t>88,51%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>95,37%</t>
+          <t>93,07%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -10809,32 +10809,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>796600</t>
+          <t>802843</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>777172</t>
+          <t>783009</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>817127</t>
+          <t>818086</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>91,35%</t>
+          <t>90,64%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>89,13%</t>
+          <t>88,4%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>93,71%</t>
+          <t>92,36%</t>
         </is>
       </c>
     </row>
@@ -10852,17 +10852,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>369658</t>
+          <t>396232</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>369658</t>
+          <t>396232</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>369658</t>
+          <t>396232</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -10887,17 +10887,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>502340</t>
+          <t>489526</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>502340</t>
+          <t>489526</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>502340</t>
+          <t>489526</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -10922,17 +10922,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>871998</t>
+          <t>885758</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>871998</t>
+          <t>885758</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>871998</t>
+          <t>885758</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -11082,22 +11082,22 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>2189</t>
+          <t>2390</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>598</t>
+          <t>664</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>5939</t>
+          <t>7000</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>1,64%</t>
+          <t>1,63%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
@@ -11107,7 +11107,7 @@
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>4,45%</t>
+          <t>4,78%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -11117,32 +11117,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>2208</t>
+          <t>2314</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>627</t>
+          <t>540</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>5408</t>
+          <t>5678</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>1,44%</t>
+          <t>1,32%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>0,41%</t>
+          <t>0,31%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>3,52%</t>
+          <t>3,23%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -11152,32 +11152,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>4397</t>
+          <t>4704</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1787</t>
+          <t>2078</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>9288</t>
+          <t>9835</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>1,53%</t>
+          <t>1,46%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>0,62%</t>
+          <t>0,64%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>3,24%</t>
+          <t>3,05%</t>
         </is>
       </c>
     </row>
@@ -11195,32 +11195,32 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>15259</t>
+          <t>16950</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>8030</t>
+          <t>9530</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>23945</t>
+          <t>26005</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>11,43%</t>
+          <t>11,58%</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>6,02%</t>
+          <t>6,51%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>17,94%</t>
+          <t>17,77%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -11230,32 +11230,32 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>23140</t>
+          <t>24177</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>16388</t>
+          <t>16824</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>32990</t>
+          <t>33416</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>15,08%</t>
+          <t>13,74%</t>
         </is>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>10,68%</t>
+          <t>9,56%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>21,5%</t>
+          <t>18,99%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -11265,32 +11265,32 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>38399</t>
+          <t>41128</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>28215</t>
+          <t>30830</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>51233</t>
+          <t>54061</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
         <is>
-          <t>13,38%</t>
+          <t>12,76%</t>
         </is>
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>9,83%</t>
+          <t>9,56%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>17,86%</t>
+          <t>16,77%</t>
         </is>
       </c>
     </row>
@@ -11308,32 +11308,32 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>11203</t>
+          <t>12161</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>6108</t>
+          <t>6672</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>20013</t>
+          <t>20438</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>8,39%</t>
+          <t>8,31%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>4,58%</t>
+          <t>4,56%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>14,99%</t>
+          <t>13,96%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -11343,32 +11343,32 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>16094</t>
+          <t>16960</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>10378</t>
+          <t>10698</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>23029</t>
+          <t>24389</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>10,49%</t>
+          <t>9,64%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>6,76%</t>
+          <t>6,08%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>15,01%</t>
+          <t>13,86%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -11378,32 +11378,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>27297</t>
+          <t>29122</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>20019</t>
+          <t>21145</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>37977</t>
+          <t>39986</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>9,51%</t>
+          <t>9,03%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>6,98%</t>
+          <t>6,56%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>13,24%</t>
+          <t>12,41%</t>
         </is>
       </c>
     </row>
@@ -11421,32 +11421,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>104833</t>
+          <t>114883</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>93810</t>
+          <t>103818</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>113136</t>
+          <t>124301</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>78,54%</t>
+          <t>78,48%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>70,28%</t>
+          <t>70,92%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>84,76%</t>
+          <t>84,91%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -11456,32 +11456,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>112014</t>
+          <t>132500</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>101887</t>
+          <t>121837</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>120775</t>
+          <t>142362</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>72,99%</t>
+          <t>75,3%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>66,39%</t>
+          <t>69,24%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>78,7%</t>
+          <t>80,91%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -11491,32 +11491,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>216846</t>
+          <t>247384</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>201040</t>
+          <t>232921</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>229556</t>
+          <t>260863</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>75,57%</t>
+          <t>76,75%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>70,06%</t>
+          <t>72,26%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>80,0%</t>
+          <t>80,93%</t>
         </is>
       </c>
     </row>
@@ -11534,17 +11534,17 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>133483</t>
+          <t>146384</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>133483</t>
+          <t>146384</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>133483</t>
+          <t>146384</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -11569,17 +11569,17 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>153456</t>
+          <t>175952</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>153456</t>
+          <t>175952</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>153456</t>
+          <t>175952</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -11604,17 +11604,17 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>286939</t>
+          <t>322337</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>286939</t>
+          <t>322337</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>286939</t>
+          <t>322337</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -11686,7 +11686,7 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>1342</t>
+          <t>1378</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
@@ -11696,7 +11696,7 @@
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>4862</t>
+          <t>5006</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -11721,7 +11721,7 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>1342</t>
+          <t>1378</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
@@ -11731,7 +11731,7 @@
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>4262</t>
+          <t>4782</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -11746,7 +11746,7 @@
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>0,28%</t>
+          <t>0,3%</t>
         </is>
       </c>
     </row>
@@ -11764,32 +11764,32 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>6762</t>
+          <t>8579</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>2680</t>
+          <t>4052</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>13732</t>
+          <t>16861</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>1,06%</t>
+          <t>1,24%</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>0,42%</t>
+          <t>0,59%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>2,14%</t>
+          <t>2,44%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -11799,32 +11799,32 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>6637</t>
+          <t>7082</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>3210</t>
+          <t>3488</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>11985</t>
+          <t>12584</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>0,74%</t>
+          <t>0,77%</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>0,36%</t>
+          <t>0,38%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>1,34%</t>
+          <t>1,36%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -11834,32 +11834,32 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>13399</t>
+          <t>15661</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>8130</t>
+          <t>8969</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>20934</t>
+          <t>25348</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>0,87%</t>
+          <t>0,97%</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>0,53%</t>
+          <t>0,56%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>1,36%</t>
+          <t>1,57%</t>
         </is>
       </c>
     </row>
@@ -11877,32 +11877,32 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>32671</t>
+          <t>34723</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>22204</t>
+          <t>22906</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>50119</t>
+          <t>52229</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>5,1%</t>
+          <t>5,03%</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>3,47%</t>
+          <t>3,32%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>7,82%</t>
+          <t>7,57%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -11912,32 +11912,32 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>44799</t>
+          <t>48972</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>31840</t>
+          <t>38578</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>58159</t>
+          <t>64088</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>5,01%</t>
+          <t>5,31%</t>
         </is>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>3,56%</t>
+          <t>4,18%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>6,51%</t>
+          <t>6,94%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -11947,32 +11947,32 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>77470</t>
+          <t>83695</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>59181</t>
+          <t>66805</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>96198</t>
+          <t>103837</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
         <is>
-          <t>5,05%</t>
+          <t>5,19%</t>
         </is>
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>3,86%</t>
+          <t>4,14%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>6,27%</t>
+          <t>6,44%</t>
         </is>
       </c>
     </row>
@@ -11990,32 +11990,32 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>26735</t>
+          <t>29321</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>18255</t>
+          <t>20027</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>37888</t>
+          <t>40708</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>4,17%</t>
+          <t>4,25%</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>2,85%</t>
+          <t>2,9%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>5,91%</t>
+          <t>5,9%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -12025,32 +12025,32 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>33871</t>
+          <t>35686</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>24088</t>
+          <t>26853</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>45361</t>
+          <t>46404</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>3,79%</t>
+          <t>3,87%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>2,7%</t>
+          <t>2,91%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>5,08%</t>
+          <t>5,03%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -12060,32 +12060,32 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>60606</t>
+          <t>65006</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>45699</t>
+          <t>51116</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>76463</t>
+          <t>80643</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>3,95%</t>
+          <t>4,03%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>2,98%</t>
+          <t>3,17%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>4,98%</t>
+          <t>5,0%</t>
         </is>
       </c>
     </row>
@@ -12103,32 +12103,32 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>574485</t>
+          <t>617134</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>556762</t>
+          <t>595891</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>590180</t>
+          <t>633362</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>89,67%</t>
+          <t>89,47%</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>86,91%</t>
+          <t>86,39%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>92,12%</t>
+          <t>91,82%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -12138,32 +12138,32 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>806750</t>
+          <t>829676</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>789926</t>
+          <t>813321</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>829885</t>
+          <t>843183</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>90,3%</t>
+          <t>89,91%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>88,42%</t>
+          <t>88,14%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>92,89%</t>
+          <t>91,37%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -12173,32 +12173,32 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>1381234</t>
+          <t>1446810</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1356380</t>
+          <t>1423090</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1408990</t>
+          <t>1468991</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>90,04%</t>
+          <t>89,72%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>88,42%</t>
+          <t>88,25%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>91,85%</t>
+          <t>91,1%</t>
         </is>
       </c>
     </row>
@@ -12216,17 +12216,17 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>640653</t>
+          <t>689757</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>640653</t>
+          <t>689757</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>640653</t>
+          <t>689757</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -12251,17 +12251,17 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>893399</t>
+          <t>922793</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>893399</t>
+          <t>922793</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>893399</t>
+          <t>922793</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -12286,17 +12286,17 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>1534051</t>
+          <t>1612550</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>1534051</t>
+          <t>1612550</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>1534051</t>
+          <t>1612550</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
